--- a/data/Data No estacional.xlsx
+++ b/data/Data No estacional.xlsx
@@ -5,21 +5,22 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Mi unidad\ANTES 2026\INVESTIGACION\INVESTIGACIÓN EXTERNA\UDEP\TESIS ECONOMETRICA\TRATADO DE DATOS\Datos procesados\contrafactual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\econometria-udep\econometria-app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C736EEE5-2791-4CE2-AC6A-155DF85BD982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C989202-2D16-4BF9-9948-FD142D9368F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2325" yWindow="1335" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="16080" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
+    <sheet name="Hoja2" sheetId="3" r:id="rId2"/>
+    <sheet name="Hoja1" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Hoja1!$A$1:$D$253</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Hoja1!$A$1:$D$253</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -3952,7 +3953,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE253"/>
+  <dimension ref="A1:AE219"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" customWidth="1"/>
@@ -24732,3242 +24733,3255 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A220" s="2">
-        <v>43891</v>
-      </c>
-      <c r="B220">
-        <v>2159.4283639800001</v>
-      </c>
-      <c r="C220">
-        <v>0.12695874925191039</v>
-      </c>
-      <c r="D220">
-        <v>4956.9658562300001</v>
-      </c>
-      <c r="E220">
-        <v>3.6257077842107473E-2</v>
-      </c>
-      <c r="F220">
-        <v>1443.19440762</v>
-      </c>
-      <c r="G220">
-        <v>3.5151683087284828E-2</v>
-      </c>
-      <c r="H220">
-        <v>14310.29253604</v>
-      </c>
-      <c r="I220">
-        <v>7.9052390781736412E-2</v>
-      </c>
-      <c r="J220">
-        <v>22869.881163869999</v>
-      </c>
-      <c r="K220">
-        <v>7.1529753897207393E-2</v>
-      </c>
-      <c r="L220">
-        <v>1.25</v>
-      </c>
-      <c r="M220">
-        <v>140.82045052103899</v>
-      </c>
-      <c r="N220">
-        <v>7.6775988193476419</v>
-      </c>
-      <c r="O220">
-        <v>-6.4474399364503832E-2</v>
-      </c>
-      <c r="P220">
-        <v>8.5085491100061308</v>
-      </c>
-      <c r="Q220">
-        <v>-1.7740092763004259E-2</v>
-      </c>
-      <c r="R220">
-        <v>7.2746142743147093</v>
-      </c>
-      <c r="S220">
-        <v>-9.6313065271873555E-3</v>
-      </c>
-      <c r="T220">
-        <v>9.5687343151116373</v>
-      </c>
-      <c r="U220">
-        <v>-2.3018160265031899E-2</v>
-      </c>
-      <c r="V220">
-        <v>10.03757609084548</v>
-      </c>
-      <c r="W220">
-        <v>-2.5032665806969941E-2</v>
-      </c>
-      <c r="X220">
-        <v>4.9250556190049064</v>
-      </c>
-      <c r="Y220">
-        <v>-0.16237033134242829</v>
-      </c>
-      <c r="Z220">
-        <v>1.8883883036171101E-2</v>
-      </c>
-      <c r="AA220">
-        <v>-2.622670470956955E-3</v>
-      </c>
-      <c r="AB220">
-        <v>-1.035601905429798E-4</v>
-      </c>
-      <c r="AC220">
-        <v>-4.4297506593844738E-4</v>
-      </c>
-      <c r="AD220">
-        <v>7.156953747072814E-4</v>
-      </c>
-      <c r="AE220">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="221" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A221" s="2">
-        <v>43922</v>
-      </c>
-      <c r="B221">
-        <v>2138.9006645700001</v>
-      </c>
-      <c r="C221">
-        <v>0.1174060293540956</v>
-      </c>
-      <c r="D221">
-        <v>4833.40990616</v>
-      </c>
-      <c r="E221">
-        <v>3.6674382661831727E-2</v>
-      </c>
-      <c r="F221">
-        <v>1435.3239125</v>
-      </c>
-      <c r="G221">
-        <v>3.6710352026549972E-2</v>
-      </c>
-      <c r="H221">
-        <v>14089.046786409999</v>
-      </c>
-      <c r="I221">
-        <v>7.9516869480526817E-2</v>
-      </c>
-      <c r="J221">
-        <v>22496.681269640001</v>
-      </c>
-      <c r="K221">
-        <v>7.1183401675834201E-2</v>
-      </c>
-      <c r="L221">
-        <v>0.25</v>
-      </c>
-      <c r="M221">
-        <v>104.571783804586</v>
-      </c>
-      <c r="N221">
-        <v>7.6680472678778022</v>
-      </c>
-      <c r="O221">
-        <v>-9.5515514698396586E-3</v>
-      </c>
-      <c r="P221">
-        <v>8.4833074822688559</v>
-      </c>
-      <c r="Q221">
-        <v>-2.52416277372749E-2</v>
-      </c>
-      <c r="R221">
-        <v>7.2691458257186348</v>
-      </c>
-      <c r="S221">
-        <v>-5.4684485960745377E-3</v>
-      </c>
-      <c r="T221">
-        <v>9.5531529508235451</v>
-      </c>
-      <c r="U221">
-        <v>-1.55813642880922E-2</v>
-      </c>
-      <c r="V221">
-        <v>10.02112307818633</v>
-      </c>
-      <c r="W221">
-        <v>-1.645301265914334E-2</v>
-      </c>
-      <c r="X221">
-        <v>4.6344532220542991</v>
-      </c>
-      <c r="Y221">
-        <v>-0.29060239695060641</v>
-      </c>
-      <c r="Z221">
-        <v>-9.5527198978147959E-3</v>
-      </c>
-      <c r="AA221">
-        <v>4.1730481972425398E-4</v>
-      </c>
-      <c r="AB221">
-        <v>1.558668939265144E-3</v>
-      </c>
-      <c r="AC221">
-        <v>4.6447869879040482E-4</v>
-      </c>
-      <c r="AD221">
-        <v>-3.4635222137319183E-4</v>
-      </c>
-      <c r="AE221">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="222" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A222" s="2">
-        <v>43952</v>
-      </c>
-      <c r="B222">
-        <v>2183.1003610900002</v>
-      </c>
-      <c r="C222">
-        <v>0.1124785327905852</v>
-      </c>
-      <c r="D222">
-        <v>4733.6882485699998</v>
-      </c>
-      <c r="E222">
-        <v>3.7745282498055449E-2</v>
-      </c>
-      <c r="F222">
-        <v>1428.6810697999999</v>
-      </c>
-      <c r="G222">
-        <v>3.6032640088950393E-2</v>
-      </c>
-      <c r="H222">
-        <v>14087.11798673</v>
-      </c>
-      <c r="I222">
-        <v>7.8700272163145985E-2</v>
-      </c>
-      <c r="J222">
-        <v>22432.58766619</v>
-      </c>
-      <c r="K222">
-        <v>7.0627852643051409E-2</v>
-      </c>
-      <c r="L222">
-        <v>0.25</v>
-      </c>
-      <c r="M222">
-        <v>116.20409231795</v>
-      </c>
-      <c r="N222">
-        <v>7.6885013294235467</v>
-      </c>
-      <c r="O222">
-        <v>2.045406154574447E-2</v>
-      </c>
-      <c r="P222">
-        <v>8.4624599342024798</v>
-      </c>
-      <c r="Q222">
-        <v>-2.084754806637612E-2</v>
-      </c>
-      <c r="R222">
-        <v>7.2645069688358266</v>
-      </c>
-      <c r="S222">
-        <v>-4.6388568828081844E-3</v>
-      </c>
-      <c r="T222">
-        <v>9.5530160408005855</v>
-      </c>
-      <c r="U222">
-        <v>-1.369100229595688E-4</v>
-      </c>
-      <c r="V222">
-        <v>10.018269987163681</v>
-      </c>
-      <c r="W222">
-        <v>-2.853091022650744E-3</v>
-      </c>
-      <c r="X222">
-        <v>4.7711480763772691</v>
-      </c>
-      <c r="Y222">
-        <v>0.13669485432296999</v>
-      </c>
-      <c r="Z222">
-        <v>-4.9274965635103954E-3</v>
-      </c>
-      <c r="AA222">
-        <v>1.0708998362237219E-3</v>
-      </c>
-      <c r="AB222">
-        <v>-6.7771193759957882E-4</v>
-      </c>
-      <c r="AC222">
-        <v>-8.1659731738083219E-4</v>
-      </c>
-      <c r="AD222">
-        <v>-5.5554903278279277E-4</v>
-      </c>
-      <c r="AE222">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="223" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A223" s="2">
-        <v>43983</v>
-      </c>
-      <c r="B223">
-        <v>2204.0703212399999</v>
-      </c>
-      <c r="C223">
-        <v>0.11094637160779269</v>
-      </c>
-      <c r="D223">
-        <v>4646.4947893199997</v>
-      </c>
-      <c r="E223">
-        <v>3.8160728975217321E-2</v>
-      </c>
-      <c r="F223">
-        <v>1420.3440982899999</v>
-      </c>
-      <c r="G223">
-        <v>3.7407814911870563E-2</v>
-      </c>
-      <c r="H223">
-        <v>14248.5252177</v>
-      </c>
-      <c r="I223">
-        <v>7.7194744944105012E-2</v>
-      </c>
-      <c r="J223">
-        <v>22519.43442655</v>
-      </c>
-      <c r="K223">
-        <v>6.9934725827005356E-2</v>
-      </c>
-      <c r="L223">
-        <v>0.25</v>
-      </c>
-      <c r="M223">
-        <v>139.91102445364899</v>
-      </c>
-      <c r="N223">
-        <v>7.6980610759525607</v>
-      </c>
-      <c r="O223">
-        <v>9.5597465290140349E-3</v>
-      </c>
-      <c r="P223">
-        <v>8.4438684055763407</v>
-      </c>
-      <c r="Q223">
-        <v>-1.8591528626139109E-2</v>
-      </c>
-      <c r="R223">
-        <v>7.2586544439793306</v>
-      </c>
-      <c r="S223">
-        <v>-5.8525248564960108E-3</v>
-      </c>
-      <c r="T223">
-        <v>9.5644086868462388</v>
-      </c>
-      <c r="U223">
-        <v>1.139264604565327E-2</v>
-      </c>
-      <c r="V223">
-        <v>10.02213396766428</v>
-      </c>
-      <c r="W223">
-        <v>3.863980500595332E-3</v>
-      </c>
-      <c r="X223">
-        <v>4.9373683015533629</v>
-      </c>
-      <c r="Y223">
-        <v>0.16622022517609381</v>
-      </c>
-      <c r="Z223">
-        <v>-1.532161182792507E-3</v>
-      </c>
-      <c r="AA223">
-        <v>4.1544647716187239E-4</v>
-      </c>
-      <c r="AB223">
-        <v>1.3751748229201689E-3</v>
-      </c>
-      <c r="AC223">
-        <v>-1.505527219040972E-3</v>
-      </c>
-      <c r="AD223">
-        <v>-6.9312681604605242E-4</v>
-      </c>
-      <c r="AE223">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="224" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A224" s="2">
-        <v>44013</v>
-      </c>
-      <c r="B224">
-        <v>2217.3487439099999</v>
-      </c>
-      <c r="C224">
-        <v>0.1156340769146989</v>
-      </c>
-      <c r="D224">
-        <v>4608.5607300699994</v>
-      </c>
-      <c r="E224">
-        <v>3.4936834461017169E-2</v>
-      </c>
-      <c r="F224">
-        <v>1409.0320153600001</v>
-      </c>
-      <c r="G224">
-        <v>3.6914573482356793E-2</v>
-      </c>
-      <c r="H224">
-        <v>14932.27259633</v>
-      </c>
-      <c r="I224">
-        <v>6.9971061896284548E-2</v>
-      </c>
-      <c r="J224">
-        <v>23167.214085669999</v>
-      </c>
-      <c r="K224">
-        <v>6.5361781476635739E-2</v>
-      </c>
-      <c r="L224">
-        <v>0.25</v>
-      </c>
-      <c r="M224">
-        <v>152.544198892754</v>
-      </c>
-      <c r="N224">
-        <v>7.7040675016701661</v>
-      </c>
-      <c r="O224">
-        <v>6.0064257176053459E-3</v>
-      </c>
-      <c r="P224">
-        <v>8.4356708811856684</v>
-      </c>
-      <c r="Q224">
-        <v>-8.1975243906722284E-3</v>
-      </c>
-      <c r="R224">
-        <v>7.2506582336845424</v>
-      </c>
-      <c r="S224">
-        <v>-7.9962102947890301E-3</v>
-      </c>
-      <c r="T224">
-        <v>9.6112800957163511</v>
-      </c>
-      <c r="U224">
-        <v>4.6871408870112319E-2</v>
-      </c>
-      <c r="V224">
-        <v>10.050493372202871</v>
-      </c>
-      <c r="W224">
-        <v>2.8359404538585761E-2</v>
-      </c>
-      <c r="X224">
-        <v>5.0367090662676031</v>
-      </c>
-      <c r="Y224">
-        <v>9.9340764714240137E-2</v>
-      </c>
-      <c r="Z224">
-        <v>4.6877053069062091E-3</v>
-      </c>
-      <c r="AA224">
-        <v>-3.2238945142001531E-3</v>
-      </c>
-      <c r="AB224">
-        <v>-4.932414295137702E-4</v>
-      </c>
-      <c r="AC224">
-        <v>-7.2236830478204636E-3</v>
-      </c>
-      <c r="AD224">
-        <v>-4.5729443503696177E-3</v>
-      </c>
-      <c r="AE224">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="225" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A225" s="2">
-        <v>44044</v>
-      </c>
-      <c r="B225">
-        <v>2261.7211269300001</v>
-      </c>
-      <c r="C225">
-        <v>0.11143274656150851</v>
-      </c>
-      <c r="D225">
-        <v>4619.2933561999998</v>
-      </c>
-      <c r="E225">
-        <v>3.2603356746732523E-2</v>
-      </c>
-      <c r="F225">
-        <v>1401.97957561</v>
-      </c>
-      <c r="G225">
-        <v>3.6528284449306427E-2</v>
-      </c>
-      <c r="H225">
-        <v>15448.824612799999</v>
-      </c>
-      <c r="I225">
-        <v>6.5903823177358822E-2</v>
-      </c>
-      <c r="J225">
-        <v>23731.818671540001</v>
-      </c>
-      <c r="K225">
-        <v>6.2025704857388432E-2</v>
-      </c>
-      <c r="L225">
-        <v>0.25</v>
-      </c>
-      <c r="M225">
-        <v>156.36406569440399</v>
-      </c>
-      <c r="N225">
-        <v>7.7238813630147067</v>
-      </c>
-      <c r="O225">
-        <v>1.9813861344540658E-2</v>
-      </c>
-      <c r="P225">
-        <v>8.4379970191737872</v>
-      </c>
-      <c r="Q225">
-        <v>2.3261379881187589E-3</v>
-      </c>
-      <c r="R225">
-        <v>7.2456404994499044</v>
-      </c>
-      <c r="S225">
-        <v>-5.017734234637139E-3</v>
-      </c>
-      <c r="T225">
-        <v>9.6452882025904785</v>
-      </c>
-      <c r="U225">
-        <v>3.4008106874127357E-2</v>
-      </c>
-      <c r="V225">
-        <v>10.07457198667599</v>
-      </c>
-      <c r="W225">
-        <v>2.4078614473125981E-2</v>
-      </c>
-      <c r="X225">
-        <v>5.0542680547098611</v>
-      </c>
-      <c r="Y225">
-        <v>1.7558988442258009E-2</v>
-      </c>
-      <c r="Z225">
-        <v>-4.2013303531903967E-3</v>
-      </c>
-      <c r="AA225">
-        <v>-2.3334777142846458E-3</v>
-      </c>
-      <c r="AB225">
-        <v>-3.8628903305036599E-4</v>
-      </c>
-      <c r="AC225">
-        <v>-4.0672387189257253E-3</v>
-      </c>
-      <c r="AD225">
-        <v>-3.336076619247307E-3</v>
-      </c>
-      <c r="AE225">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="226" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A226" s="2">
-        <v>44075</v>
-      </c>
-      <c r="B226">
-        <v>2276.9921576400002</v>
-      </c>
-      <c r="C226">
-        <v>0.11070809773946309</v>
-      </c>
-      <c r="D226">
-        <v>4673.3158472900004</v>
-      </c>
-      <c r="E226">
-        <v>3.0915695022792341E-2</v>
-      </c>
-      <c r="F226">
-        <v>1403.2395340800001</v>
-      </c>
-      <c r="G226">
-        <v>4.1048794386886259E-2</v>
-      </c>
-      <c r="H226">
-        <v>16164.727005320001</v>
-      </c>
-      <c r="I226">
-        <v>6.2153965633279233E-2</v>
-      </c>
-      <c r="J226">
-        <v>24518.274544330001</v>
-      </c>
-      <c r="K226">
-        <v>5.9501065340153432E-2</v>
-      </c>
-      <c r="L226">
-        <v>0.25</v>
-      </c>
-      <c r="M226">
-        <v>160.26131398211101</v>
-      </c>
-      <c r="N226">
-        <v>7.7306106218944359</v>
-      </c>
-      <c r="O226">
-        <v>6.7292588797291941E-3</v>
-      </c>
-      <c r="P226">
-        <v>8.4496241302494202</v>
-      </c>
-      <c r="Q226">
-        <v>1.1627111075632969E-2</v>
-      </c>
-      <c r="R226">
-        <v>7.2465387954513636</v>
-      </c>
-      <c r="S226">
-        <v>8.9829600145918675E-4</v>
-      </c>
-      <c r="T226">
-        <v>9.6905868020070312</v>
-      </c>
-      <c r="U226">
-        <v>4.5298599416552683E-2</v>
-      </c>
-      <c r="V226">
-        <v>10.10717401825641</v>
-      </c>
-      <c r="W226">
-        <v>3.2602031580420743E-2</v>
-      </c>
-      <c r="X226">
-        <v>5.0882121949345764</v>
-      </c>
-      <c r="Y226">
-        <v>3.3944140224715369E-2</v>
-      </c>
-      <c r="Z226">
-        <v>-7.2464882204541226E-4</v>
-      </c>
-      <c r="AA226">
-        <v>-1.6876617239401819E-3</v>
-      </c>
-      <c r="AB226">
-        <v>4.5205099375798322E-3</v>
-      </c>
-      <c r="AC226">
-        <v>-3.7498575440795892E-3</v>
-      </c>
-      <c r="AD226">
-        <v>-2.524639517235E-3</v>
-      </c>
-      <c r="AE226">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="227" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A227" s="2">
-        <v>44105</v>
-      </c>
-      <c r="B227">
-        <v>2231.4262205499999</v>
-      </c>
-      <c r="C227">
-        <v>0.10771210436917709</v>
-      </c>
-      <c r="D227">
-        <v>4806.8549881299996</v>
-      </c>
-      <c r="E227">
-        <v>3.1291336042262183E-2</v>
-      </c>
-      <c r="F227">
-        <v>1404.1004755700001</v>
-      </c>
-      <c r="G227">
-        <v>4.3559165860385649E-2</v>
-      </c>
-      <c r="H227">
-        <v>16643.936121160001</v>
-      </c>
-      <c r="I227">
-        <v>5.7584737024525517E-2</v>
-      </c>
-      <c r="J227">
-        <v>25086.317805409999</v>
-      </c>
-      <c r="K227">
-        <v>5.6220393512109917E-2</v>
-      </c>
-      <c r="L227">
-        <v>0.25</v>
-      </c>
-      <c r="M227">
-        <v>166.74684518517901</v>
-      </c>
-      <c r="N227">
-        <v>7.7103962208070786</v>
-      </c>
-      <c r="O227">
-        <v>-2.0214401087357281E-2</v>
-      </c>
-      <c r="P227">
-        <v>8.4777983006259525</v>
-      </c>
-      <c r="Q227">
-        <v>2.8174170376532359E-2</v>
-      </c>
-      <c r="R227">
-        <v>7.2471521458214863</v>
-      </c>
-      <c r="S227">
-        <v>6.1335037012266724E-4</v>
-      </c>
-      <c r="T227">
-        <v>9.7198012321454552</v>
-      </c>
-      <c r="U227">
-        <v>2.921443013842406E-2</v>
-      </c>
-      <c r="V227">
-        <v>10.130077869140671</v>
-      </c>
-      <c r="W227">
-        <v>2.2903850884253171E-2</v>
-      </c>
-      <c r="X227">
-        <v>5.1376596451039553</v>
-      </c>
-      <c r="Y227">
-        <v>4.9447450169378897E-2</v>
-      </c>
-      <c r="Z227">
-        <v>-2.9959933702859991E-3</v>
-      </c>
-      <c r="AA227">
-        <v>3.7564101946984188E-4</v>
-      </c>
-      <c r="AB227">
-        <v>2.5103714734993898E-3</v>
-      </c>
-      <c r="AC227">
-        <v>-4.5692286087537157E-3</v>
-      </c>
-      <c r="AD227">
-        <v>-3.280671828043515E-3</v>
-      </c>
-      <c r="AE227">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="228" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A228" s="2">
-        <v>44136</v>
-      </c>
-      <c r="B228">
-        <v>2280.1507402299999</v>
-      </c>
-      <c r="C228">
-        <v>0.10319941129693209</v>
-      </c>
-      <c r="D228">
-        <v>4948.6570592999997</v>
-      </c>
-      <c r="E228">
-        <v>3.0511784985431639E-2</v>
-      </c>
-      <c r="F228">
-        <v>1409.1993044200001</v>
-      </c>
-      <c r="G228">
-        <v>4.370211886766949E-2</v>
-      </c>
-      <c r="H228">
-        <v>17039.103716760001</v>
-      </c>
-      <c r="I228">
-        <v>5.4603099088178682E-2</v>
-      </c>
-      <c r="J228">
-        <v>25677.110820710001</v>
-      </c>
-      <c r="K228">
-        <v>5.3677200989386442E-2</v>
-      </c>
-      <c r="L228">
-        <v>0.25</v>
-      </c>
-      <c r="M228">
-        <v>168.292170423214</v>
-      </c>
-      <c r="N228">
-        <v>7.7319968338990082</v>
-      </c>
-      <c r="O228">
-        <v>2.160061309192951E-2</v>
-      </c>
-      <c r="P228">
-        <v>8.5068715176024057</v>
-      </c>
-      <c r="Q228">
-        <v>2.907321697645315E-2</v>
-      </c>
-      <c r="R228">
-        <v>7.2507769528677546</v>
-      </c>
-      <c r="S228">
-        <v>3.6248070462692179E-3</v>
-      </c>
-      <c r="T228">
-        <v>9.7432662002182528</v>
-      </c>
-      <c r="U228">
-        <v>2.3464968072797628E-2</v>
-      </c>
-      <c r="V228">
-        <v>10.153355244492809</v>
-      </c>
-      <c r="W228">
-        <v>2.327737535214958E-2</v>
-      </c>
-      <c r="X228">
-        <v>5.1373730790035861</v>
-      </c>
-      <c r="Y228">
-        <v>-2.8656610036925661E-4</v>
-      </c>
-      <c r="Z228">
-        <v>-4.5126930722449998E-3</v>
-      </c>
-      <c r="AA228">
-        <v>-7.795510568305436E-4</v>
-      </c>
-      <c r="AB228">
-        <v>1.4295300728384139E-4</v>
-      </c>
-      <c r="AC228">
-        <v>-2.9816379363468361E-3</v>
-      </c>
-      <c r="AD228">
-        <v>-2.5431925227234749E-3</v>
-      </c>
-      <c r="AE228">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="229" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A229" s="2">
-        <v>44166</v>
-      </c>
-      <c r="B229">
-        <v>2300.3196402100002</v>
-      </c>
-      <c r="C229">
-        <v>0.101678955690109</v>
-      </c>
-      <c r="D229">
-        <v>5069.7182674599999</v>
-      </c>
-      <c r="E229">
-        <v>2.6994189913548239E-2</v>
-      </c>
-      <c r="F229">
-        <v>1416.1758750700001</v>
-      </c>
-      <c r="G229">
-        <v>4.279667385027601E-2</v>
-      </c>
-      <c r="H229">
-        <v>17303.47789563</v>
-      </c>
-      <c r="I229">
-        <v>4.9784130401181181E-2</v>
-      </c>
-      <c r="J229">
-        <v>26089.69167837</v>
-      </c>
-      <c r="K229">
-        <v>4.9551879317600647E-2</v>
-      </c>
-      <c r="L229">
-        <v>0.25</v>
-      </c>
-      <c r="M229">
-        <v>172.400120770981</v>
-      </c>
-      <c r="N229">
-        <v>7.7408033662655971</v>
-      </c>
-      <c r="O229">
-        <v>8.8065323665889039E-3</v>
-      </c>
-      <c r="P229">
-        <v>8.5310405264929159</v>
-      </c>
-      <c r="Q229">
-        <v>2.4169008890510209E-2</v>
-      </c>
-      <c r="R229">
-        <v>7.2557154720987027</v>
-      </c>
-      <c r="S229">
-        <v>4.9385192309472359E-3</v>
-      </c>
-      <c r="T229">
-        <v>9.7586627947106361</v>
-      </c>
-      <c r="U229">
-        <v>1.539659449238329E-2</v>
-      </c>
-      <c r="V229">
-        <v>10.16929556044385</v>
-      </c>
-      <c r="W229">
-        <v>1.594031595103651E-2</v>
-      </c>
-      <c r="X229">
-        <v>5.2531473915789588</v>
-      </c>
-      <c r="Y229">
-        <v>0.1157743125753727</v>
-      </c>
-      <c r="Z229">
-        <v>-1.5204556068230961E-3</v>
-      </c>
-      <c r="AA229">
-        <v>-3.5175950718833999E-3</v>
-      </c>
-      <c r="AB229">
-        <v>-9.0544501739348027E-4</v>
-      </c>
-      <c r="AC229">
-        <v>-4.8189686869975004E-3</v>
-      </c>
-      <c r="AD229">
-        <v>-4.1253216717857949E-3</v>
-      </c>
-      <c r="AE229">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="230" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A230" s="2">
-        <v>44197</v>
-      </c>
-      <c r="B230">
-        <v>2275.7306163899998</v>
-      </c>
-      <c r="C230">
-        <v>0.1052414975766867</v>
-      </c>
-      <c r="D230">
-        <v>5112.7377065800001</v>
-      </c>
-      <c r="E230">
-        <v>2.6677292383777761E-2</v>
-      </c>
-      <c r="F230">
-        <v>1409.5821437</v>
-      </c>
-      <c r="G230">
-        <v>4.2525803819176179E-2</v>
-      </c>
-      <c r="H230">
-        <v>17303.545139239999</v>
-      </c>
-      <c r="I230">
-        <v>5.1406725220879752E-2</v>
-      </c>
-      <c r="J230">
-        <v>26101.595605909999</v>
-      </c>
-      <c r="K230">
-        <v>5.0776876665727999E-2</v>
-      </c>
-      <c r="L230">
-        <v>0.25</v>
-      </c>
-      <c r="M230">
-        <v>172.90099314200501</v>
-      </c>
-      <c r="N230">
-        <v>7.730056429888946</v>
-      </c>
-      <c r="O230">
-        <v>-1.074693637665103E-2</v>
-      </c>
-      <c r="P230">
-        <v>8.5394902944447626</v>
-      </c>
-      <c r="Q230">
-        <v>8.4497679518467095E-3</v>
-      </c>
-      <c r="R230">
-        <v>7.2510485874654709</v>
-      </c>
-      <c r="S230">
-        <v>-4.6668846332318381E-3</v>
-      </c>
-      <c r="T230">
-        <v>9.758666680835713</v>
-      </c>
-      <c r="U230">
-        <v>3.8861250768462696E-6</v>
-      </c>
-      <c r="V230">
-        <v>10.16975172576821</v>
-      </c>
-      <c r="W230">
-        <v>4.5616532436021368E-4</v>
-      </c>
-      <c r="X230">
-        <v>5.0818272569195218</v>
-      </c>
-      <c r="Y230">
-        <v>-0.1713201346594371</v>
-      </c>
-      <c r="Z230">
-        <v>3.562541886577703E-3</v>
-      </c>
-      <c r="AA230">
-        <v>-3.168975297704775E-4</v>
-      </c>
-      <c r="AB230">
-        <v>-2.7087003109983049E-4</v>
-      </c>
-      <c r="AC230">
-        <v>1.6225948196985709E-3</v>
-      </c>
-      <c r="AD230">
-        <v>1.2249973481273521E-3</v>
-      </c>
-      <c r="AE230">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="231" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A231" s="2">
-        <v>44228</v>
-      </c>
-      <c r="B231">
-        <v>2279.78727114</v>
-      </c>
-      <c r="C231">
-        <v>0.1030168990515333</v>
-      </c>
-      <c r="D231">
-        <v>5152.0684472299999</v>
-      </c>
-      <c r="E231">
-        <v>2.6486224526649459E-2</v>
-      </c>
-      <c r="F231">
-        <v>1410.2242385100001</v>
-      </c>
-      <c r="G231">
-        <v>4.2750860993354352E-2</v>
-      </c>
-      <c r="H231">
-        <v>17292.186950200001</v>
-      </c>
-      <c r="I231">
-        <v>5.8556908493768538E-2</v>
-      </c>
-      <c r="J231">
-        <v>26134.26690708</v>
-      </c>
-      <c r="K231">
-        <v>5.5260045030716312E-2</v>
-      </c>
-      <c r="L231">
-        <v>0.25</v>
-      </c>
-      <c r="M231">
-        <v>169.15538756642201</v>
-      </c>
-      <c r="N231">
-        <v>7.7318374154639926</v>
-      </c>
-      <c r="O231">
-        <v>1.7809855750465791E-3</v>
-      </c>
-      <c r="P231">
-        <v>8.5471535532607668</v>
-      </c>
-      <c r="Q231">
-        <v>7.6632588160041593E-3</v>
-      </c>
-      <c r="R231">
-        <v>7.2515040051318387</v>
-      </c>
-      <c r="S231">
-        <v>4.5541766636780778E-4</v>
-      </c>
-      <c r="T231">
-        <v>9.7580100570984989</v>
-      </c>
-      <c r="U231">
-        <v>-6.566237372140904E-4</v>
-      </c>
-      <c r="V231">
-        <v>10.17100264051752</v>
-      </c>
-      <c r="W231">
-        <v>1.250914749313381E-3</v>
-      </c>
-      <c r="X231">
-        <v>5.0485044532861796</v>
-      </c>
-      <c r="Y231">
-        <v>-3.3322803633342168E-2</v>
-      </c>
-      <c r="Z231">
-        <v>-2.2245985251534012E-3</v>
-      </c>
-      <c r="AA231">
-        <v>-1.9106785712830199E-4</v>
-      </c>
-      <c r="AB231">
-        <v>2.2505717417817259E-4</v>
-      </c>
-      <c r="AC231">
-        <v>7.1501832728887854E-3</v>
-      </c>
-      <c r="AD231">
-        <v>4.4831683649883131E-3</v>
-      </c>
-      <c r="AE231">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="232" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A232" s="2">
-        <v>44256</v>
-      </c>
-      <c r="B232">
-        <v>2271.0733725499999</v>
-      </c>
-      <c r="C232">
-        <v>9.826505070570403E-2</v>
-      </c>
-      <c r="D232">
-        <v>5229.7713057399997</v>
-      </c>
-      <c r="E232">
-        <v>2.6958617246849309E-2</v>
-      </c>
-      <c r="F232">
-        <v>1410.99503755</v>
-      </c>
-      <c r="G232">
-        <v>4.2955943746791667E-2</v>
-      </c>
-      <c r="H232">
-        <v>17410.84239396</v>
-      </c>
-      <c r="I232">
-        <v>6.3918540870605292E-2</v>
-      </c>
-      <c r="J232">
-        <v>26322.6821098</v>
-      </c>
-      <c r="K232">
-        <v>5.8415050610193427E-2</v>
-      </c>
-      <c r="L232">
-        <v>0.25</v>
-      </c>
-      <c r="M232">
-        <v>168.75683535705301</v>
-      </c>
-      <c r="N232">
-        <v>7.7280078500600933</v>
-      </c>
-      <c r="O232">
-        <v>-3.8295654038993381E-3</v>
-      </c>
-      <c r="P232">
-        <v>8.5621228287109297</v>
-      </c>
-      <c r="Q232">
-        <v>1.4969275450162909E-2</v>
-      </c>
-      <c r="R232">
-        <v>7.2520504348728521</v>
-      </c>
-      <c r="S232">
-        <v>5.4642974101337671E-4</v>
-      </c>
-      <c r="T232">
-        <v>9.7648484172298264</v>
-      </c>
-      <c r="U232">
-        <v>6.8383601313275477E-3</v>
-      </c>
-      <c r="V232">
-        <v>10.17818628411519</v>
-      </c>
-      <c r="W232">
-        <v>7.1836435976635471E-3</v>
-      </c>
-      <c r="X232">
-        <v>5.1063229783943678</v>
-      </c>
-      <c r="Y232">
-        <v>5.781852510818819E-2</v>
-      </c>
-      <c r="Z232">
-        <v>-4.751848345829271E-3</v>
-      </c>
-      <c r="AA232">
-        <v>4.7239272019984971E-4</v>
-      </c>
-      <c r="AB232">
-        <v>2.050827534373148E-4</v>
-      </c>
-      <c r="AC232">
-        <v>5.3616323768367544E-3</v>
-      </c>
-      <c r="AD232">
-        <v>3.155005579477115E-3</v>
-      </c>
-      <c r="AE232">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="233" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A233" s="2">
-        <v>44287</v>
-      </c>
-      <c r="B233">
-        <v>2280.2364451200001</v>
-      </c>
-      <c r="C233">
-        <v>9.9853541937409723E-2</v>
-      </c>
-      <c r="D233">
-        <v>5299.7645609700003</v>
-      </c>
-      <c r="E233">
-        <v>2.8025877446302049E-2</v>
-      </c>
-      <c r="F233">
-        <v>1414.0914274300001</v>
-      </c>
-      <c r="G233">
-        <v>4.3759021969647802E-2</v>
-      </c>
-      <c r="H233">
-        <v>17590.599337340002</v>
-      </c>
-      <c r="I233">
-        <v>6.6101338952208197E-2</v>
-      </c>
-      <c r="J233">
-        <v>26584.691770860001</v>
-      </c>
-      <c r="K233">
-        <v>6.0217424312766929E-2</v>
-      </c>
-      <c r="L233">
-        <v>0.25</v>
-      </c>
-      <c r="M233">
-        <v>167.832160638837</v>
-      </c>
-      <c r="N233">
-        <v>7.7320344205715994</v>
-      </c>
-      <c r="O233">
-        <v>4.0265705115052342E-3</v>
-      </c>
-      <c r="P233">
-        <v>8.5754176760950163</v>
-      </c>
-      <c r="Q233">
-        <v>1.3294847384086589E-2</v>
-      </c>
-      <c r="R233">
-        <v>7.2542425030861768</v>
-      </c>
-      <c r="S233">
-        <v>2.1920682133247378E-3</v>
-      </c>
-      <c r="T233">
-        <v>9.7751199097685415</v>
-      </c>
-      <c r="U233">
-        <v>1.0271492538715069E-2</v>
-      </c>
-      <c r="V233">
-        <v>10.18809083177155</v>
-      </c>
-      <c r="W233">
-        <v>9.9045476563581758E-3</v>
-      </c>
-      <c r="X233">
-        <v>5.1038408364617132</v>
-      </c>
-      <c r="Y233">
-        <v>-2.482141932654613E-3</v>
-      </c>
-      <c r="Z233">
-        <v>1.5884912317056939E-3</v>
-      </c>
-      <c r="AA233">
-        <v>1.067260199452739E-3</v>
-      </c>
-      <c r="AB233">
-        <v>8.0307822285613506E-4</v>
-      </c>
-      <c r="AC233">
-        <v>2.1827980816029051E-3</v>
-      </c>
-      <c r="AD233">
-        <v>1.8023737025735021E-3</v>
-      </c>
-      <c r="AE233">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="234" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A234" s="2">
-        <v>44317</v>
-      </c>
-      <c r="B234">
-        <v>2276.4251643399998</v>
-      </c>
-      <c r="C234">
-        <v>9.7517738785127928E-2</v>
-      </c>
-      <c r="D234">
-        <v>5333.5101946000004</v>
-      </c>
-      <c r="E234">
-        <v>3.2891037969255521E-2</v>
-      </c>
-      <c r="F234">
-        <v>1414.1026799700001</v>
-      </c>
-      <c r="G234">
-        <v>4.5129050290289997E-2</v>
-      </c>
-      <c r="H234">
-        <v>17861.444640760001</v>
-      </c>
-      <c r="I234">
-        <v>6.6689788999582042E-2</v>
-      </c>
-      <c r="J234">
-        <v>26885.48267967</v>
-      </c>
-      <c r="K234">
-        <v>6.1461035527158411E-2</v>
-      </c>
-      <c r="L234">
-        <v>0.25</v>
-      </c>
-      <c r="M234">
-        <v>172.46262082341099</v>
-      </c>
-      <c r="N234">
-        <v>7.7303615811134847</v>
-      </c>
-      <c r="O234">
-        <v>-1.672839458113806E-3</v>
-      </c>
-      <c r="P234">
-        <v>8.581764873491478</v>
-      </c>
-      <c r="Q234">
-        <v>6.3471973964617234E-3</v>
-      </c>
-      <c r="R234">
-        <v>7.2542504604890796</v>
-      </c>
-      <c r="S234">
-        <v>7.9574029028250948E-6</v>
-      </c>
-      <c r="T234">
-        <v>9.7903997380999677</v>
-      </c>
-      <c r="U234">
-        <v>1.527982833142616E-2</v>
-      </c>
-      <c r="V234">
-        <v>10.19934174257601</v>
-      </c>
-      <c r="W234">
-        <v>1.125091080446694E-2</v>
-      </c>
-      <c r="X234">
-        <v>5.1672691739430272</v>
-      </c>
-      <c r="Y234">
-        <v>6.3428337481314045E-2</v>
-      </c>
-      <c r="Z234">
-        <v>-2.3358031522817961E-3</v>
-      </c>
-      <c r="AA234">
-        <v>4.8651605229534734E-3</v>
-      </c>
-      <c r="AB234">
-        <v>1.3700283206421961E-3</v>
-      </c>
-      <c r="AC234">
-        <v>5.8845004737384521E-4</v>
-      </c>
-      <c r="AD234">
-        <v>1.2436112143914819E-3</v>
-      </c>
-      <c r="AE234">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="235" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A235" s="2">
-        <v>44348</v>
-      </c>
-      <c r="B235">
-        <v>2286.9315393799998</v>
-      </c>
-      <c r="C235">
-        <v>9.1658109978590793E-2</v>
-      </c>
-      <c r="D235">
-        <v>5358.6517146100005</v>
-      </c>
-      <c r="E235">
-        <v>3.1368390944630307E-2</v>
-      </c>
-      <c r="F235">
-        <v>1408.03971073</v>
-      </c>
-      <c r="G235">
-        <v>4.4266246424034192E-2</v>
-      </c>
-      <c r="H235">
-        <v>18024.676300989999</v>
-      </c>
-      <c r="I235">
-        <v>6.267882312027695E-2</v>
-      </c>
-      <c r="J235">
-        <v>27078.29926571</v>
-      </c>
-      <c r="K235">
-        <v>5.7972704250960252E-2</v>
-      </c>
-      <c r="L235">
-        <v>0.25</v>
-      </c>
-      <c r="M235">
-        <v>172.756272866323</v>
-      </c>
-      <c r="N235">
-        <v>7.7349662588917383</v>
-      </c>
-      <c r="O235">
-        <v>4.6046777782535742E-3</v>
-      </c>
-      <c r="P235">
-        <v>8.5864676766401846</v>
-      </c>
-      <c r="Q235">
-        <v>4.7028031487066357E-3</v>
-      </c>
-      <c r="R235">
-        <v>7.2499537399637379</v>
-      </c>
-      <c r="S235">
-        <v>-4.2967205253416907E-3</v>
-      </c>
-      <c r="T235">
-        <v>9.7994970036556968</v>
-      </c>
-      <c r="U235">
-        <v>9.0972655557290949E-3</v>
-      </c>
-      <c r="V235">
-        <v>10.20648792098121</v>
-      </c>
-      <c r="W235">
-        <v>7.1461784051916064E-3</v>
-      </c>
-      <c r="X235">
-        <v>5.1477490955581402</v>
-      </c>
-      <c r="Y235">
-        <v>-1.9520078384887011E-2</v>
-      </c>
-      <c r="Z235">
-        <v>-5.8596288065371344E-3</v>
-      </c>
-      <c r="AA235">
-        <v>-1.522647024625214E-3</v>
-      </c>
-      <c r="AB235">
-        <v>-8.6280386625580546E-4</v>
-      </c>
-      <c r="AC235">
-        <v>-4.0109658793050923E-3</v>
-      </c>
-      <c r="AD235">
-        <v>-3.4883312761981589E-3</v>
-      </c>
-      <c r="AE235">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="236" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A236" s="2">
-        <v>44378</v>
-      </c>
-      <c r="B236">
-        <v>2262.2419197999998</v>
-      </c>
-      <c r="C236">
-        <v>9.8105483802378254E-2</v>
-      </c>
-      <c r="D236">
-        <v>5368.7611469200001</v>
-      </c>
-      <c r="E236">
-        <v>3.2271793767431257E-2</v>
-      </c>
-      <c r="F236">
-        <v>1409.3347980000001</v>
-      </c>
-      <c r="G236">
-        <v>4.3749786947359537E-2</v>
-      </c>
-      <c r="H236">
-        <v>18214.69351021</v>
-      </c>
-      <c r="I236">
-        <v>6.5127595126157206E-2</v>
-      </c>
-      <c r="J236">
-        <v>27255.03137493</v>
-      </c>
-      <c r="K236">
-        <v>6.0287407098030543E-2</v>
-      </c>
-      <c r="L236">
-        <v>0.25</v>
-      </c>
-      <c r="M236">
-        <v>173.54042175974399</v>
-      </c>
-      <c r="N236">
-        <v>7.7241116004710788</v>
-      </c>
-      <c r="O236">
-        <v>-1.085465842065947E-2</v>
-      </c>
-      <c r="P236">
-        <v>8.5883524619902474</v>
-      </c>
-      <c r="Q236">
-        <v>1.8847853500627561E-3</v>
-      </c>
-      <c r="R236">
-        <v>7.2508730975835407</v>
-      </c>
-      <c r="S236">
-        <v>9.193576198027742E-4</v>
-      </c>
-      <c r="T236">
-        <v>9.8099838830705224</v>
-      </c>
-      <c r="U236">
-        <v>1.0486879414825619E-2</v>
-      </c>
-      <c r="V236">
-        <v>10.212993420660069</v>
-      </c>
-      <c r="W236">
-        <v>6.5054996788695973E-3</v>
-      </c>
-      <c r="X236">
-        <v>5.1617476485985376</v>
-      </c>
-      <c r="Y236">
-        <v>1.3998553040397431E-2</v>
-      </c>
-      <c r="Z236">
-        <v>6.4473738237874612E-3</v>
-      </c>
-      <c r="AA236">
-        <v>9.0340282280094997E-4</v>
-      </c>
-      <c r="AB236">
-        <v>-5.1645947667465497E-4</v>
-      </c>
-      <c r="AC236">
-        <v>2.448772005880256E-3</v>
-      </c>
-      <c r="AD236">
-        <v>2.3147028470702912E-3</v>
-      </c>
-      <c r="AE236">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="237" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A237" s="2">
-        <v>44409</v>
-      </c>
-      <c r="B237">
-        <v>2234.4294547300001</v>
-      </c>
-      <c r="C237">
-        <v>9.8231403616420049E-2</v>
-      </c>
-      <c r="D237">
-        <v>5406.58861299</v>
-      </c>
-      <c r="E237">
-        <v>3.0962517930030201E-2</v>
-      </c>
-      <c r="F237">
-        <v>1274.8114010700001</v>
-      </c>
-      <c r="G237">
-        <v>3.31111587287116E-2</v>
-      </c>
-      <c r="H237">
-        <v>18427.78186173</v>
-      </c>
-      <c r="I237">
-        <v>6.3027044009135183E-2</v>
-      </c>
-      <c r="J237">
-        <v>27343.611330520002</v>
-      </c>
-      <c r="K237">
-        <v>5.8169047983602687E-2</v>
-      </c>
-      <c r="L237">
-        <v>0.5</v>
-      </c>
-      <c r="M237">
-        <v>174.87920486451901</v>
-      </c>
-      <c r="N237">
-        <v>7.7117411969330876</v>
-      </c>
-      <c r="O237">
-        <v>-1.237040353799035E-2</v>
-      </c>
-      <c r="P237">
-        <v>8.5953736023354335</v>
-      </c>
-      <c r="Q237">
-        <v>7.0211403451860832E-3</v>
-      </c>
-      <c r="R237">
-        <v>7.1505535259217652</v>
-      </c>
-      <c r="S237">
-        <v>-0.10031957166177551</v>
-      </c>
-      <c r="T237">
-        <v>9.8216146886583093</v>
-      </c>
-      <c r="U237">
-        <v>1.163080558778695E-2</v>
-      </c>
-      <c r="V237">
-        <v>10.21623819118618</v>
-      </c>
-      <c r="W237">
-        <v>3.2447705261073878E-3</v>
-      </c>
-      <c r="X237">
-        <v>5.1677028585334774</v>
-      </c>
-      <c r="Y237">
-        <v>5.9552099349398091E-3</v>
-      </c>
-      <c r="Z237">
-        <v>1.2591981404179439E-4</v>
-      </c>
-      <c r="AA237">
-        <v>-1.3092758374010571E-3</v>
-      </c>
-      <c r="AB237">
-        <v>-1.0638628218647941E-2</v>
-      </c>
-      <c r="AC237">
-        <v>-2.1005511170220231E-3</v>
-      </c>
-      <c r="AD237">
-        <v>-2.1183591144278559E-3</v>
-      </c>
-      <c r="AE237">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="238" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A238" s="2">
-        <v>44440</v>
-      </c>
-      <c r="B238">
-        <v>2202.2242701199998</v>
-      </c>
-      <c r="C238">
-        <v>0.1005012039976927</v>
-      </c>
-      <c r="D238">
-        <v>5473.4202434999997</v>
-      </c>
-      <c r="E238">
-        <v>3.062295816570073E-2</v>
-      </c>
-      <c r="F238">
-        <v>1277.1083010699999</v>
-      </c>
-      <c r="G238">
-        <v>3.2102560257145203E-2</v>
-      </c>
-      <c r="H238">
-        <v>18797.73941237</v>
-      </c>
-      <c r="I238">
-        <v>6.1177140654117099E-2</v>
-      </c>
-      <c r="J238">
-        <v>27750.49222706</v>
-      </c>
-      <c r="K238">
-        <v>5.6933365038454462E-2</v>
-      </c>
-      <c r="L238">
-        <v>1</v>
-      </c>
-      <c r="M238">
-        <v>175.854950933071</v>
-      </c>
-      <c r="N238">
-        <v>7.6972231604706369</v>
-      </c>
-      <c r="O238">
-        <v>-1.451803646245153E-2</v>
-      </c>
-      <c r="P238">
-        <v>8.6076589730490269</v>
-      </c>
-      <c r="Q238">
-        <v>1.228537071359348E-2</v>
-      </c>
-      <c r="R238">
-        <v>7.1523536614184504</v>
-      </c>
-      <c r="S238">
-        <v>1.800135496684341E-3</v>
-      </c>
-      <c r="T238">
-        <v>9.8414918975652768</v>
-      </c>
-      <c r="U238">
-        <v>1.9877208906967429E-2</v>
-      </c>
-      <c r="V238">
-        <v>10.231008856929339</v>
-      </c>
-      <c r="W238">
-        <v>1.477066574315522E-2</v>
-      </c>
-      <c r="X238">
-        <v>5.1837894023935513</v>
-      </c>
-      <c r="Y238">
-        <v>1.608654386007391E-2</v>
-      </c>
-      <c r="Z238">
-        <v>2.2698003812726551E-3</v>
-      </c>
-      <c r="AA238">
-        <v>-3.3955976432947088E-4</v>
-      </c>
-      <c r="AB238">
-        <v>-1.008598471566396E-3</v>
-      </c>
-      <c r="AC238">
-        <v>-1.8499033550180839E-3</v>
-      </c>
-      <c r="AD238">
-        <v>-1.235682945148225E-3</v>
-      </c>
-      <c r="AE238">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="239" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A239" s="2">
-        <v>44470</v>
-      </c>
-      <c r="B239">
-        <v>2194.2493606399998</v>
-      </c>
-      <c r="C239">
-        <v>0.1004161101114477</v>
-      </c>
-      <c r="D239">
-        <v>5571.17602627</v>
-      </c>
-      <c r="E239">
-        <v>2.930325374753975E-2</v>
-      </c>
-      <c r="F239">
-        <v>1285.5089196199999</v>
-      </c>
-      <c r="G239">
-        <v>3.1440552673837073E-2</v>
-      </c>
-      <c r="H239">
-        <v>19083.164364209999</v>
-      </c>
-      <c r="I239">
-        <v>6.1382550182132331E-2</v>
-      </c>
-      <c r="J239">
-        <v>28134.098670740001</v>
-      </c>
-      <c r="K239">
-        <v>5.6706347481436388E-2</v>
-      </c>
-      <c r="L239">
-        <v>1.5</v>
-      </c>
-      <c r="M239">
-        <v>175.023326475673</v>
-      </c>
-      <c r="N239">
-        <v>7.6935952900924418</v>
-      </c>
-      <c r="O239">
-        <v>-3.6278703781951189E-3</v>
-      </c>
-      <c r="P239">
-        <v>8.6253614464108921</v>
-      </c>
-      <c r="Q239">
-        <v>1.7702473361865149E-2</v>
-      </c>
-      <c r="R239">
-        <v>7.1589099653205341</v>
-      </c>
-      <c r="S239">
-        <v>6.5563039020846148E-3</v>
-      </c>
-      <c r="T239">
-        <v>9.8565617784319723</v>
-      </c>
-      <c r="U239">
-        <v>1.5069880866695581E-2</v>
-      </c>
-      <c r="V239">
-        <v>10.244737595482169</v>
-      </c>
-      <c r="W239">
-        <v>1.372873855283707E-2</v>
-      </c>
-      <c r="X239">
-        <v>5.1842126201835352</v>
-      </c>
-      <c r="Y239">
-        <v>4.2321778998388743E-4</v>
-      </c>
-      <c r="Z239">
-        <v>-8.5093886245002359E-5</v>
-      </c>
-      <c r="AA239">
-        <v>-1.319704418160979E-3</v>
-      </c>
-      <c r="AB239">
-        <v>-6.6200758330813014E-4</v>
-      </c>
-      <c r="AC239">
-        <v>2.0540952801523241E-4</v>
-      </c>
-      <c r="AD239">
-        <v>-2.270175570180735E-4</v>
-      </c>
-      <c r="AE239">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="240" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A240" s="2">
-        <v>44501</v>
-      </c>
-      <c r="B240">
-        <v>2172.2655704700001</v>
-      </c>
-      <c r="C240">
-        <v>9.8535122012585449E-2</v>
-      </c>
-      <c r="D240">
-        <v>5670.17393722</v>
-      </c>
-      <c r="E240">
-        <v>2.8580077620943781E-2</v>
-      </c>
-      <c r="F240">
-        <v>1300.8241159700001</v>
-      </c>
-      <c r="G240">
-        <v>3.1301938325180197E-2</v>
-      </c>
-      <c r="H240">
-        <v>19422.658219389999</v>
-      </c>
-      <c r="I240">
-        <v>5.9420327775620327E-2</v>
-      </c>
-      <c r="J240">
-        <v>28565.92184305</v>
-      </c>
-      <c r="K240">
-        <v>5.499271148437309E-2</v>
-      </c>
-      <c r="L240">
-        <v>2</v>
-      </c>
-      <c r="M240">
-        <v>174.28334484974999</v>
-      </c>
-      <c r="N240">
-        <v>7.6835259435932697</v>
-      </c>
-      <c r="O240">
-        <v>-1.0069346499172131E-2</v>
-      </c>
-      <c r="P240">
-        <v>8.6429750730096533</v>
-      </c>
-      <c r="Q240">
-        <v>1.7613626598761201E-2</v>
-      </c>
-      <c r="R240">
-        <v>7.170753277959026</v>
-      </c>
-      <c r="S240">
-        <v>1.184331263849181E-2</v>
-      </c>
-      <c r="T240">
-        <v>9.8741956129821542</v>
-      </c>
-      <c r="U240">
-        <v>1.7633834550181859E-2</v>
-      </c>
-      <c r="V240">
-        <v>10.25996974240574</v>
-      </c>
-      <c r="W240">
-        <v>1.523214692356412E-2</v>
-      </c>
-      <c r="X240">
-        <v>5.1742099993998973</v>
-      </c>
-      <c r="Y240">
-        <v>-1.0002620783637889E-2</v>
-      </c>
-      <c r="Z240">
-        <v>-1.880988098862252E-3</v>
-      </c>
-      <c r="AA240">
-        <v>-7.231761265959688E-4</v>
-      </c>
-      <c r="AB240">
-        <v>-1.3861434865687641E-4</v>
-      </c>
-      <c r="AC240">
-        <v>-1.9622224065120042E-3</v>
-      </c>
-      <c r="AD240">
-        <v>-1.7136359970632981E-3</v>
-      </c>
-      <c r="AE240">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="241" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A241" s="2">
-        <v>44531</v>
-      </c>
-      <c r="B241">
-        <v>2169.81716056</v>
-      </c>
-      <c r="C241">
-        <v>9.1217174736012499E-2</v>
-      </c>
-      <c r="D241">
-        <v>5749.7459773599994</v>
-      </c>
-      <c r="E241">
-        <v>2.502358037668688E-2</v>
-      </c>
-      <c r="F241">
-        <v>1388.26564278</v>
-      </c>
-      <c r="G241">
-        <v>2.809212703118107E-2</v>
-      </c>
-      <c r="H241">
-        <v>19628.150631429999</v>
-      </c>
-      <c r="I241">
-        <v>5.4190274307697628E-2</v>
-      </c>
-      <c r="J241">
-        <v>28935.97941213</v>
-      </c>
-      <c r="K241">
-        <v>4.9919099083422812E-2</v>
-      </c>
-      <c r="L241">
-        <v>2.5</v>
-      </c>
-      <c r="M241">
-        <v>175.225814954611</v>
-      </c>
-      <c r="N241">
-        <v>7.6823981851781653</v>
-      </c>
-      <c r="O241">
-        <v>-1.127758415104374E-3</v>
-      </c>
-      <c r="P241">
-        <v>8.6569109549650918</v>
-      </c>
-      <c r="Q241">
-        <v>1.3935881955438489E-2</v>
-      </c>
-      <c r="R241">
-        <v>7.2358105080431061</v>
-      </c>
-      <c r="S241">
-        <v>6.5057230084080153E-2</v>
-      </c>
-      <c r="T241">
-        <v>9.8847200714940815</v>
-      </c>
-      <c r="U241">
-        <v>1.0524458511927289E-2</v>
-      </c>
-      <c r="V241">
-        <v>10.27284106213493</v>
-      </c>
-      <c r="W241">
-        <v>1.28713197291912E-2</v>
-      </c>
-      <c r="X241">
-        <v>5.273232864679092</v>
-      </c>
-      <c r="Y241">
-        <v>9.9022865279194683E-2</v>
-      </c>
-      <c r="Z241">
-        <v>-7.3179472765729503E-3</v>
-      </c>
-      <c r="AA241">
-        <v>-3.5564972442569021E-3</v>
-      </c>
-      <c r="AB241">
-        <v>-3.209811293999127E-3</v>
-      </c>
-      <c r="AC241">
-        <v>-5.230053467922699E-3</v>
-      </c>
-      <c r="AD241">
-        <v>-5.0736124009502781E-3</v>
-      </c>
-      <c r="AE241">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="242" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A242" s="2">
-        <v>44562</v>
-      </c>
-      <c r="B242">
-        <v>2163.45077055</v>
-      </c>
-      <c r="C242">
-        <v>9.3923785091879819E-2</v>
-      </c>
-      <c r="D242">
-        <v>5802.8133554100004</v>
-      </c>
-      <c r="E242">
-        <v>2.7455609970888549E-2</v>
-      </c>
-      <c r="F242">
-        <v>1385.66927007</v>
-      </c>
-      <c r="G242">
-        <v>2.9273104979769728E-2</v>
-      </c>
-      <c r="H242">
-        <v>19591.822615789999</v>
-      </c>
-      <c r="I242">
-        <v>5.9054299032267298E-2</v>
-      </c>
-      <c r="J242">
-        <v>28943.756011820002</v>
-      </c>
-      <c r="K242">
-        <v>5.389982758847553E-2</v>
-      </c>
-      <c r="L242">
-        <v>3</v>
-      </c>
-      <c r="M242">
-        <v>177.77595236253299</v>
-      </c>
-      <c r="N242">
-        <v>7.6794598048647984</v>
-      </c>
-      <c r="O242">
-        <v>-2.9383803133669062E-3</v>
-      </c>
-      <c r="P242">
-        <v>8.6660981402079038</v>
-      </c>
-      <c r="Q242">
-        <v>9.1871852428120349E-3</v>
-      </c>
-      <c r="R242">
-        <v>7.2339385293920007</v>
-      </c>
-      <c r="S242">
-        <v>-1.8719786511054439E-3</v>
-      </c>
-      <c r="T242">
-        <v>9.8828675446807477</v>
-      </c>
-      <c r="U242">
-        <v>-1.85252681333381E-3</v>
-      </c>
-      <c r="V242">
-        <v>10.27310977793606</v>
-      </c>
-      <c r="W242">
-        <v>2.6871580112874938E-4</v>
-      </c>
-      <c r="X242">
-        <v>5.1119546552775281</v>
-      </c>
-      <c r="Y242">
-        <v>-0.1612782094015639</v>
-      </c>
-      <c r="Z242">
-        <v>2.7066103558673199E-3</v>
-      </c>
-      <c r="AA242">
-        <v>2.4320295942016688E-3</v>
-      </c>
-      <c r="AB242">
-        <v>1.1809779485886589E-3</v>
-      </c>
-      <c r="AC242">
-        <v>4.8640247245696697E-3</v>
-      </c>
-      <c r="AD242">
-        <v>3.9807285050527177E-3</v>
-      </c>
-      <c r="AE242">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="243" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A243" s="2">
-        <v>44593</v>
-      </c>
-      <c r="B243">
-        <v>2159.5255895599998</v>
-      </c>
-      <c r="C243">
-        <v>9.7333164277449757E-2</v>
-      </c>
-      <c r="D243">
-        <v>5914.4869055199997</v>
-      </c>
-      <c r="E243">
-        <v>2.795292140822898E-2</v>
-      </c>
-      <c r="F243">
-        <v>1394.5299547</v>
-      </c>
-      <c r="G243">
-        <v>2.907100487398372E-2</v>
-      </c>
-      <c r="H243">
-        <v>19819.768310349999</v>
-      </c>
-      <c r="I243">
-        <v>6.09586301843437E-2</v>
-      </c>
-      <c r="J243">
-        <v>29288.31076013</v>
-      </c>
-      <c r="K243">
-        <v>5.5457174495057507E-2</v>
-      </c>
-      <c r="L243">
-        <v>3.5</v>
-      </c>
-      <c r="M243">
-        <v>177.45500302739299</v>
-      </c>
-      <c r="N243">
-        <v>7.677643842092067</v>
-      </c>
-      <c r="O243">
-        <v>-1.8159627727314389E-3</v>
-      </c>
-      <c r="P243">
-        <v>8.6851600280210448</v>
-      </c>
-      <c r="Q243">
-        <v>1.9061887813140999E-2</v>
-      </c>
-      <c r="R243">
-        <v>7.2403126874392054</v>
-      </c>
-      <c r="S243">
-        <v>6.3741580472047588E-3</v>
-      </c>
-      <c r="T243">
-        <v>9.894435118125946</v>
-      </c>
-      <c r="U243">
-        <v>1.156757344519832E-2</v>
-      </c>
-      <c r="V243">
-        <v>10.284943765237159</v>
-      </c>
-      <c r="W243">
-        <v>1.183398730109886E-2</v>
-      </c>
-      <c r="X243">
-        <v>5.0956937097421706</v>
-      </c>
-      <c r="Y243">
-        <v>-1.6260945535357511E-2</v>
-      </c>
-      <c r="Z243">
-        <v>3.409379185569938E-3</v>
-      </c>
-      <c r="AA243">
-        <v>4.9731143734043151E-4</v>
-      </c>
-      <c r="AB243">
-        <v>-2.0210010578600859E-4</v>
-      </c>
-      <c r="AC243">
-        <v>1.904331152076402E-3</v>
-      </c>
-      <c r="AD243">
-        <v>1.5573469065819771E-3</v>
-      </c>
-      <c r="AE243">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="244" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A244" s="2">
-        <v>44621</v>
-      </c>
-      <c r="B244">
-        <v>2154.9887514900001</v>
-      </c>
-      <c r="C244">
-        <v>9.9443574817654645E-2</v>
-      </c>
-      <c r="D244">
-        <v>6025.3310061599996</v>
-      </c>
-      <c r="E244">
-        <v>2.7902767824393208E-2</v>
-      </c>
-      <c r="F244">
-        <v>1402.4647080100001</v>
-      </c>
-      <c r="G244">
-        <v>2.8875945946235711E-2</v>
-      </c>
-      <c r="H244">
-        <v>20139.74479144</v>
-      </c>
-      <c r="I244">
-        <v>6.1288311514484932E-2</v>
-      </c>
-      <c r="J244">
-        <v>29722.529257099999</v>
-      </c>
-      <c r="K244">
-        <v>5.5757423287727863E-2</v>
-      </c>
-      <c r="L244">
-        <v>4</v>
-      </c>
-      <c r="M244">
-        <v>175.624506747689</v>
-      </c>
-      <c r="N244">
-        <v>7.6755407827980084</v>
-      </c>
-      <c r="O244">
-        <v>-2.1030592940594062E-3</v>
-      </c>
-      <c r="P244">
-        <v>8.7037276956315193</v>
-      </c>
-      <c r="Q244">
-        <v>1.8567667610474459E-2</v>
-      </c>
-      <c r="R244">
-        <v>7.2459864734510084</v>
-      </c>
-      <c r="S244">
-        <v>5.673786011803017E-3</v>
-      </c>
-      <c r="T244">
-        <v>9.9104504944663478</v>
-      </c>
-      <c r="U244">
-        <v>1.601537634040184E-2</v>
-      </c>
-      <c r="V244">
-        <v>10.299660598074039</v>
-      </c>
-      <c r="W244">
-        <v>1.4716832836885629E-2</v>
-      </c>
-      <c r="X244">
-        <v>5.1444672248879924</v>
-      </c>
-      <c r="Y244">
-        <v>4.8773515145821733E-2</v>
-      </c>
-      <c r="Z244">
-        <v>2.1104105402048878E-3</v>
-      </c>
-      <c r="AA244">
-        <v>-5.0153583835772092E-5</v>
-      </c>
-      <c r="AB244">
-        <v>-1.9505892774800829E-4</v>
-      </c>
-      <c r="AC244">
-        <v>3.2968133014123208E-4</v>
-      </c>
-      <c r="AD244">
-        <v>3.0024879267035592E-4</v>
-      </c>
-      <c r="AE244">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="245" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A245" s="2">
-        <v>44652</v>
-      </c>
-      <c r="B245">
-        <v>2160.2823818900001</v>
-      </c>
-      <c r="C245">
-        <v>0.10388968486779419</v>
-      </c>
-      <c r="D245">
-        <v>6109.3115564</v>
-      </c>
-      <c r="E245">
-        <v>2.7698388439975741E-2</v>
-      </c>
-      <c r="F245">
-        <v>1409.32815132</v>
-      </c>
-      <c r="G245">
-        <v>2.899783176240598E-2</v>
-      </c>
-      <c r="H245">
-        <v>20322.691519280001</v>
-      </c>
-      <c r="I245">
-        <v>6.1166226027724493E-2</v>
-      </c>
-      <c r="J245">
-        <v>30001.613608889998</v>
-      </c>
-      <c r="K245">
-        <v>5.5916290567881458E-2</v>
-      </c>
-      <c r="L245">
-        <v>4.5</v>
-      </c>
-      <c r="M245">
-        <v>175.36384503404199</v>
-      </c>
-      <c r="N245">
-        <v>7.6779942244899626</v>
-      </c>
-      <c r="O245">
-        <v>2.453441691955049E-3</v>
-      </c>
-      <c r="P245">
-        <v>8.7175693709237319</v>
-      </c>
-      <c r="Q245">
-        <v>1.384167529221259E-2</v>
-      </c>
-      <c r="R245">
-        <v>7.2508683813899983</v>
-      </c>
-      <c r="S245">
-        <v>4.8819079389899036E-3</v>
-      </c>
-      <c r="T245">
-        <v>9.9194933495782909</v>
-      </c>
-      <c r="U245">
-        <v>9.0428551119430267E-3</v>
-      </c>
-      <c r="V245">
-        <v>10.309006446160829</v>
-      </c>
-      <c r="W245">
-        <v>9.3458480867827376E-3</v>
-      </c>
-      <c r="X245">
-        <v>5.1434736132675161</v>
-      </c>
-      <c r="Y245">
-        <v>-9.9361162047628682E-4</v>
-      </c>
-      <c r="Z245">
-        <v>4.4461100501395484E-3</v>
-      </c>
-      <c r="AA245">
-        <v>-2.043793844174677E-4</v>
-      </c>
-      <c r="AB245">
-        <v>1.218858161702689E-4</v>
-      </c>
-      <c r="AC245">
-        <v>-1.2208548676043851E-4</v>
-      </c>
-      <c r="AD245">
-        <v>1.588672801535948E-4</v>
-      </c>
-      <c r="AE245">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="246" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A246" s="2">
-        <v>44682</v>
-      </c>
-      <c r="B246">
-        <v>2154.5626099599999</v>
-      </c>
-      <c r="C246">
-        <v>0.1014939018476979</v>
-      </c>
-      <c r="D246">
-        <v>6210.7306745899996</v>
-      </c>
-      <c r="E246">
-        <v>2.7251930952741449E-2</v>
-      </c>
-      <c r="F246">
-        <v>1469.05325739</v>
-      </c>
-      <c r="G246">
-        <v>4.2067353759383641E-2</v>
-      </c>
-      <c r="H246">
-        <v>20483.47195363</v>
-      </c>
-      <c r="I246">
-        <v>5.9320679424401293E-2</v>
-      </c>
-      <c r="J246">
-        <v>30317.818495570002</v>
-      </c>
-      <c r="K246">
-        <v>5.4912329069562227E-2</v>
-      </c>
-      <c r="L246">
-        <v>5</v>
-      </c>
-      <c r="M246">
-        <v>176.549094020246</v>
-      </c>
-      <c r="N246">
-        <v>7.6753430167218442</v>
-      </c>
-      <c r="O246">
-        <v>-2.6512077681184461E-3</v>
-      </c>
-      <c r="P246">
-        <v>8.7340338289705901</v>
-      </c>
-      <c r="Q246">
-        <v>1.6464458046858251E-2</v>
-      </c>
-      <c r="R246">
-        <v>7.2923734296964247</v>
-      </c>
-      <c r="S246">
-        <v>4.1505048306426318E-2</v>
-      </c>
-      <c r="T246">
-        <v>9.92737359377087</v>
-      </c>
-      <c r="U246">
-        <v>7.8802441925791555E-3</v>
-      </c>
-      <c r="V246">
-        <v>10.319490887813281</v>
-      </c>
-      <c r="W246">
-        <v>1.0484441652451441E-2</v>
-      </c>
-      <c r="X246">
-        <v>5.1923644532351414</v>
-      </c>
-      <c r="Y246">
-        <v>4.8890839967625332E-2</v>
-      </c>
-      <c r="Z246">
-        <v>-2.3957830200962982E-3</v>
-      </c>
-      <c r="AA246">
-        <v>-4.4645748723429191E-4</v>
-      </c>
-      <c r="AB246">
-        <v>1.3069521996977661E-2</v>
-      </c>
-      <c r="AC246">
-        <v>-1.8455466033232E-3</v>
-      </c>
-      <c r="AD246">
-        <v>-1.003961498319231E-3</v>
-      </c>
-      <c r="AE246">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="247" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A247" s="2">
-        <v>44713</v>
-      </c>
-      <c r="B247">
-        <v>2171.5867223400001</v>
-      </c>
-      <c r="C247">
-        <v>0.1021520059079033</v>
-      </c>
-      <c r="D247">
-        <v>6276.0739399699996</v>
-      </c>
-      <c r="E247">
-        <v>2.6874319215048351E-2</v>
-      </c>
-      <c r="F247">
-        <v>1473.95082613</v>
-      </c>
-      <c r="G247">
-        <v>4.1859331021236047E-2</v>
-      </c>
-      <c r="H247">
-        <v>20658.609303699999</v>
-      </c>
-      <c r="I247">
-        <v>5.8381463019584218E-2</v>
-      </c>
-      <c r="J247">
-        <v>30580.22079214</v>
-      </c>
-      <c r="K247">
-        <v>5.4227063829317558E-2</v>
-      </c>
-      <c r="L247">
-        <v>5.5</v>
-      </c>
-      <c r="M247">
-        <v>179.22937448249701</v>
-      </c>
-      <c r="N247">
-        <v>7.6832133877834643</v>
-      </c>
-      <c r="O247">
-        <v>7.8703710616201406E-3</v>
-      </c>
-      <c r="P247">
-        <v>8.744499895168163</v>
-      </c>
-      <c r="Q247">
-        <v>1.046606619757284E-2</v>
-      </c>
-      <c r="R247">
-        <v>7.2957017113583316</v>
-      </c>
-      <c r="S247">
-        <v>3.3282816619077948E-3</v>
-      </c>
-      <c r="T247">
-        <v>9.9358874269375015</v>
-      </c>
-      <c r="U247">
-        <v>8.5138331666314571E-3</v>
-      </c>
-      <c r="V247">
-        <v>10.328108699605449</v>
-      </c>
-      <c r="W247">
-        <v>8.6178117921740238E-3</v>
-      </c>
-      <c r="X247">
-        <v>5.1842933195331096</v>
-      </c>
-      <c r="Y247">
-        <v>-8.0711337020318297E-3</v>
-      </c>
-      <c r="Z247">
-        <v>6.581040602054028E-4</v>
-      </c>
-      <c r="AA247">
-        <v>-3.776117376930975E-4</v>
-      </c>
-      <c r="AB247">
-        <v>-2.0802273814759381E-4</v>
-      </c>
-      <c r="AC247">
-        <v>-9.3921640481707536E-4</v>
-      </c>
-      <c r="AD247">
-        <v>-6.8526524024466878E-4</v>
-      </c>
-      <c r="AE247">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="248" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A248" s="2">
-        <v>44743</v>
-      </c>
-      <c r="B248">
-        <v>2167.5417105699999</v>
-      </c>
-      <c r="C248">
-        <v>0.1105223508372544</v>
-      </c>
-      <c r="D248">
-        <v>6331.3028230299997</v>
-      </c>
-      <c r="E248">
-        <v>2.7757695861701681E-2</v>
-      </c>
-      <c r="F248">
-        <v>1477.4233848900001</v>
-      </c>
-      <c r="G248">
-        <v>4.1208457787158252E-2</v>
-      </c>
-      <c r="H248">
-        <v>20863.02957418</v>
-      </c>
-      <c r="I248">
-        <v>5.9807626479340903E-2</v>
-      </c>
-      <c r="J248">
-        <v>30839.297492670001</v>
-      </c>
-      <c r="K248">
-        <v>5.5901234558269557E-2</v>
-      </c>
-      <c r="L248">
-        <v>6</v>
-      </c>
-      <c r="M248">
-        <v>177.76735736691001</v>
-      </c>
-      <c r="N248">
-        <v>7.6813489521004517</v>
-      </c>
-      <c r="O248">
-        <v>-1.8644356830126441E-3</v>
-      </c>
-      <c r="P248">
-        <v>8.7532613111850921</v>
-      </c>
-      <c r="Q248">
-        <v>8.7614160169291466E-3</v>
-      </c>
-      <c r="R248">
-        <v>7.2980548933773832</v>
-      </c>
-      <c r="S248">
-        <v>2.3531820190507702E-3</v>
-      </c>
-      <c r="T248">
-        <v>9.9457339516709293</v>
-      </c>
-      <c r="U248">
-        <v>9.8465247334278416E-3</v>
-      </c>
-      <c r="V248">
-        <v>10.33654504832151</v>
-      </c>
-      <c r="W248">
-        <v>8.4363487160636907E-3</v>
-      </c>
-      <c r="X248">
-        <v>5.1814829433165821</v>
-      </c>
-      <c r="Y248">
-        <v>-2.8103762165274659E-3</v>
-      </c>
-      <c r="Z248">
-        <v>8.3703449293510979E-3</v>
-      </c>
-      <c r="AA248">
-        <v>8.8337664665332979E-4</v>
-      </c>
-      <c r="AB248">
-        <v>-6.5087323407779507E-4</v>
-      </c>
-      <c r="AC248">
-        <v>1.426163459756685E-3</v>
-      </c>
-      <c r="AD248">
-        <v>1.674170728951999E-3</v>
-      </c>
-      <c r="AE248">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="249" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A249" s="2">
-        <v>44774</v>
-      </c>
-      <c r="B249">
-        <v>2183.1975619300001</v>
-      </c>
-      <c r="C249">
-        <v>0.11121653208761929</v>
-      </c>
-      <c r="D249">
-        <v>6404.7049425300002</v>
-      </c>
-      <c r="E249">
-        <v>2.750088030915953E-2</v>
-      </c>
-      <c r="F249">
-        <v>1487.36756025</v>
-      </c>
-      <c r="G249">
-        <v>4.0985748815009493E-2</v>
-      </c>
-      <c r="H249">
-        <v>21115.346774969999</v>
-      </c>
-      <c r="I249">
-        <v>6.0149252036226841E-2</v>
-      </c>
-      <c r="J249">
-        <v>31190.616839679999</v>
-      </c>
-      <c r="K249">
-        <v>5.6105843720721811E-2</v>
-      </c>
-      <c r="L249">
-        <v>6.5</v>
-      </c>
-      <c r="M249">
-        <v>177.59760674853001</v>
-      </c>
-      <c r="N249">
-        <v>7.6885458526520249</v>
-      </c>
-      <c r="O249">
-        <v>7.1969005515732931E-3</v>
-      </c>
-      <c r="P249">
-        <v>8.7647881465296837</v>
-      </c>
-      <c r="Q249">
-        <v>1.152683534459165E-2</v>
-      </c>
-      <c r="R249">
-        <v>7.3047630983298726</v>
-      </c>
-      <c r="S249">
-        <v>6.7082049524893614E-3</v>
-      </c>
-      <c r="T249">
-        <v>9.9577553903906555</v>
-      </c>
-      <c r="U249">
-        <v>1.2021438719726159E-2</v>
-      </c>
-      <c r="V249">
-        <v>10.347872586247581</v>
-      </c>
-      <c r="W249">
-        <v>1.132753792606955E-2</v>
-      </c>
-      <c r="X249">
-        <v>5.1875924883910596</v>
-      </c>
-      <c r="Y249">
-        <v>6.1095450744774737E-3</v>
-      </c>
-      <c r="Z249">
-        <v>6.9418125036489753E-4</v>
-      </c>
-      <c r="AA249">
-        <v>-2.5681555254215138E-4</v>
-      </c>
-      <c r="AB249">
-        <v>-2.2270897214875929E-4</v>
-      </c>
-      <c r="AC249">
-        <v>3.4162555688593832E-4</v>
-      </c>
-      <c r="AD249">
-        <v>2.0460916245225449E-4</v>
-      </c>
-      <c r="AE249">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="250" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A250" s="2">
-        <v>44805</v>
-      </c>
-      <c r="B250">
-        <v>2199.7633651400001</v>
-      </c>
-      <c r="C250">
-        <v>0.10735566742424139</v>
-      </c>
-      <c r="D250">
-        <v>6489.5910629800001</v>
-      </c>
-      <c r="E250">
-        <v>2.7683018923153009E-2</v>
-      </c>
-      <c r="F250">
-        <v>1497.1359020499999</v>
-      </c>
-      <c r="G250">
-        <v>3.972146793659212E-2</v>
-      </c>
-      <c r="H250">
-        <v>21407.916797350001</v>
-      </c>
-      <c r="I250">
-        <v>6.1088183416888257E-2</v>
-      </c>
-      <c r="J250">
-        <v>31594.40712752</v>
-      </c>
-      <c r="K250">
-        <v>5.6435549268683501E-2</v>
-      </c>
-      <c r="L250">
-        <v>6.75</v>
-      </c>
-      <c r="M250">
-        <v>179.26037297873199</v>
-      </c>
-      <c r="N250">
-        <v>7.6961050722612754</v>
-      </c>
-      <c r="O250">
-        <v>7.5592196092504338E-3</v>
-      </c>
-      <c r="P250">
-        <v>8.7779547973862453</v>
-      </c>
-      <c r="Q250">
-        <v>1.3166650856561549E-2</v>
-      </c>
-      <c r="R250">
-        <v>7.3113091632316394</v>
-      </c>
-      <c r="S250">
-        <v>6.5460649017667896E-3</v>
-      </c>
-      <c r="T250">
-        <v>9.9715160763990092</v>
-      </c>
-      <c r="U250">
-        <v>1.376068600835367E-2</v>
-      </c>
-      <c r="V250">
-        <v>10.36073539427505</v>
-      </c>
-      <c r="W250">
-        <v>1.286280802746198E-2</v>
-      </c>
-      <c r="X250">
-        <v>5.2052059676522777</v>
-      </c>
-      <c r="Y250">
-        <v>1.7613479261218149E-2</v>
-      </c>
-      <c r="Z250">
-        <v>-3.8608646633778998E-3</v>
-      </c>
-      <c r="AA250">
-        <v>1.8213861399347939E-4</v>
-      </c>
-      <c r="AB250">
-        <v>-1.2642808784173729E-3</v>
-      </c>
-      <c r="AC250">
-        <v>9.3893138066141607E-4</v>
-      </c>
-      <c r="AD250">
-        <v>3.2970554796168949E-4</v>
-      </c>
-      <c r="AE250">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="251" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A251" s="2">
-        <v>44835</v>
-      </c>
-      <c r="B251">
-        <v>2203.08783657</v>
-      </c>
-      <c r="C251">
-        <v>0.1167990055996227</v>
-      </c>
-      <c r="D251">
-        <v>6579.0635725500006</v>
-      </c>
-      <c r="E251">
-        <v>2.768095673065727E-2</v>
-      </c>
-      <c r="F251">
-        <v>1505.2793700499999</v>
-      </c>
-      <c r="G251">
-        <v>3.9623908097550557E-2</v>
-      </c>
-      <c r="H251">
-        <v>21706.975802270001</v>
-      </c>
-      <c r="I251">
-        <v>6.3164004349081995E-2</v>
-      </c>
-      <c r="J251">
-        <v>31994.406581439998</v>
-      </c>
-      <c r="K251">
-        <v>5.8453273802080541E-2</v>
-      </c>
-      <c r="L251">
-        <v>7</v>
-      </c>
-      <c r="M251">
-        <v>178.96693481014299</v>
-      </c>
-      <c r="N251">
-        <v>7.6976152173511254</v>
-      </c>
-      <c r="O251">
-        <v>1.510145089849146E-3</v>
-      </c>
-      <c r="P251">
-        <v>8.7916476999896087</v>
-      </c>
-      <c r="Q251">
-        <v>1.369290260336342E-2</v>
-      </c>
-      <c r="R251">
-        <v>7.3167337878964407</v>
-      </c>
-      <c r="S251">
-        <v>5.4246246648013141E-3</v>
-      </c>
-      <c r="T251">
-        <v>9.9853889534119702</v>
-      </c>
-      <c r="U251">
-        <v>1.387287701296103E-2</v>
-      </c>
-      <c r="V251">
-        <v>10.37331637217356</v>
-      </c>
-      <c r="W251">
-        <v>1.258097789850865E-2</v>
-      </c>
-      <c r="X251">
-        <v>5.2100373670151896</v>
-      </c>
-      <c r="Y251">
-        <v>4.8313993629118812E-3</v>
-      </c>
-      <c r="Z251">
-        <v>9.4433381753813023E-3</v>
-      </c>
-      <c r="AA251">
-        <v>-2.062192495738691E-6</v>
-      </c>
-      <c r="AB251">
-        <v>-9.7559839041562457E-5</v>
-      </c>
-      <c r="AC251">
-        <v>2.0758209321937379E-3</v>
-      </c>
-      <c r="AD251">
-        <v>2.0177245333970399E-3</v>
-      </c>
-      <c r="AE251">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="252" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A252" s="2">
-        <v>44866</v>
-      </c>
-      <c r="B252">
-        <v>2208.6535991800001</v>
-      </c>
-      <c r="C252">
-        <v>0.112432755178175</v>
-      </c>
-      <c r="D252">
-        <v>6676.3844705000001</v>
-      </c>
-      <c r="E252">
-        <v>2.7402804257062E-2</v>
-      </c>
-      <c r="F252">
-        <v>1508.91184572</v>
-      </c>
-      <c r="G252">
-        <v>3.9345624257904312E-2</v>
-      </c>
-      <c r="H252">
-        <v>22105.60582493</v>
-      </c>
-      <c r="I252">
-        <v>6.4014908517191979E-2</v>
-      </c>
-      <c r="J252">
-        <v>32499.555740330001</v>
-      </c>
-      <c r="K252">
-        <v>5.8638773235139899E-2</v>
-      </c>
-      <c r="L252">
-        <v>7.25</v>
-      </c>
-      <c r="M252">
-        <v>177.723455970728</v>
-      </c>
-      <c r="N252">
-        <v>7.7001383777148256</v>
-      </c>
-      <c r="O252">
-        <v>2.5231603637019262E-3</v>
-      </c>
-      <c r="P252">
-        <v>8.8063318730725602</v>
-      </c>
-      <c r="Q252">
-        <v>1.468417308295145E-2</v>
-      </c>
-      <c r="R252">
-        <v>7.3191440380554278</v>
-      </c>
-      <c r="S252">
-        <v>2.4102501589871039E-3</v>
-      </c>
-      <c r="T252">
-        <v>10.003586512576939</v>
-      </c>
-      <c r="U252">
-        <v>1.8197559164967458E-2</v>
-      </c>
-      <c r="V252">
-        <v>10.388981698696091</v>
-      </c>
-      <c r="W252">
-        <v>1.5665326522537271E-2</v>
-      </c>
-      <c r="X252">
-        <v>5.1961971509984943</v>
-      </c>
-      <c r="Y252">
-        <v>-1.3840216016695271E-2</v>
-      </c>
-      <c r="Z252">
-        <v>-4.3662504214476983E-3</v>
-      </c>
-      <c r="AA252">
-        <v>-2.781524735952709E-4</v>
-      </c>
-      <c r="AB252">
-        <v>-2.7828383964624559E-4</v>
-      </c>
-      <c r="AC252">
-        <v>8.5090416810998382E-4</v>
-      </c>
-      <c r="AD252">
-        <v>1.854994330593579E-4</v>
-      </c>
-      <c r="AE252">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="253" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A253" s="2">
-        <v>44896</v>
-      </c>
-      <c r="B253">
-        <v>2234.6737479899998</v>
-      </c>
-      <c r="C253">
-        <v>0.1029223141037361</v>
-      </c>
-      <c r="D253">
-        <v>6749.00415419</v>
-      </c>
-      <c r="E253">
-        <v>2.541808343879863E-2</v>
-      </c>
-      <c r="F253">
-        <v>1513.8221178900001</v>
-      </c>
-      <c r="G253">
-        <v>3.7173050779859877E-2</v>
-      </c>
-      <c r="H253">
-        <v>22169.33574626</v>
-      </c>
-      <c r="I253">
-        <v>5.8095715359323653E-2</v>
-      </c>
-      <c r="J253">
-        <v>32666.835766330001</v>
-      </c>
-      <c r="K253">
-        <v>5.3441397333297017E-2</v>
-      </c>
-      <c r="L253">
-        <v>7.5</v>
-      </c>
-      <c r="M253">
-        <v>178.01322374453099</v>
-      </c>
-      <c r="N253">
-        <v>7.7118505223387288</v>
-      </c>
-      <c r="O253">
-        <v>1.1712144623902351E-2</v>
-      </c>
-      <c r="P253">
-        <v>8.817150240269962</v>
-      </c>
-      <c r="Q253">
-        <v>1.0818367197401811E-2</v>
-      </c>
-      <c r="R253">
-        <v>7.3223929356085993</v>
-      </c>
-      <c r="S253">
-        <v>3.248897553171481E-3</v>
-      </c>
-      <c r="T253">
-        <v>10.006465340332889</v>
-      </c>
-      <c r="U253">
-        <v>2.878827755957047E-3</v>
-      </c>
-      <c r="V253">
-        <v>10.39411564549151</v>
-      </c>
-      <c r="W253">
-        <v>5.1339467954143458E-3</v>
-      </c>
-      <c r="X253">
-        <v>5.286361175301324</v>
-      </c>
-      <c r="Y253">
-        <v>9.016402430282966E-2</v>
-      </c>
-      <c r="Z253">
-        <v>-9.510441074438894E-3</v>
-      </c>
-      <c r="AA253">
-        <v>-1.9847208182633691E-3</v>
-      </c>
-      <c r="AB253">
-        <v>-2.172573478044434E-3</v>
-      </c>
-      <c r="AC253">
-        <v>-5.9191931578683257E-3</v>
-      </c>
-      <c r="AD253">
-        <v>-5.1973759018428822E-3</v>
-      </c>
-      <c r="AE253">
-        <v>0.25</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A3337E6-675E-4E79-BD24-D8A25E849C26}">
+  <dimension ref="A1:AE34"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A1" s="2">
+        <v>43891</v>
+      </c>
+      <c r="B1">
+        <v>2159.4283639800001</v>
+      </c>
+      <c r="C1">
+        <v>0.12695874925191039</v>
+      </c>
+      <c r="D1">
+        <v>4956.9658562300001</v>
+      </c>
+      <c r="E1">
+        <v>3.6257077842107473E-2</v>
+      </c>
+      <c r="F1">
+        <v>1443.19440762</v>
+      </c>
+      <c r="G1">
+        <v>3.5151683087284828E-2</v>
+      </c>
+      <c r="H1">
+        <v>14310.29253604</v>
+      </c>
+      <c r="I1">
+        <v>7.9052390781736412E-2</v>
+      </c>
+      <c r="J1">
+        <v>22869.881163869999</v>
+      </c>
+      <c r="K1">
+        <v>7.1529753897207393E-2</v>
+      </c>
+      <c r="L1">
+        <v>1.25</v>
+      </c>
+      <c r="M1">
+        <v>140.82045052103899</v>
+      </c>
+      <c r="N1">
+        <v>7.6775988193476419</v>
+      </c>
+      <c r="O1">
+        <v>-6.4474399364503832E-2</v>
+      </c>
+      <c r="P1">
+        <v>8.5085491100061308</v>
+      </c>
+      <c r="Q1">
+        <v>-1.7740092763004259E-2</v>
+      </c>
+      <c r="R1">
+        <v>7.2746142743147093</v>
+      </c>
+      <c r="S1">
+        <v>-9.6313065271873555E-3</v>
+      </c>
+      <c r="T1">
+        <v>9.5687343151116373</v>
+      </c>
+      <c r="U1">
+        <v>-2.3018160265031899E-2</v>
+      </c>
+      <c r="V1">
+        <v>10.03757609084548</v>
+      </c>
+      <c r="W1">
+        <v>-2.5032665806969941E-2</v>
+      </c>
+      <c r="X1">
+        <v>4.9250556190049064</v>
+      </c>
+      <c r="Y1">
+        <v>-0.16237033134242829</v>
+      </c>
+      <c r="Z1">
+        <v>1.8883883036171101E-2</v>
+      </c>
+      <c r="AA1">
+        <v>-2.622670470956955E-3</v>
+      </c>
+      <c r="AB1">
+        <v>-1.035601905429798E-4</v>
+      </c>
+      <c r="AC1">
+        <v>-4.4297506593844738E-4</v>
+      </c>
+      <c r="AD1">
+        <v>7.156953747072814E-4</v>
+      </c>
+      <c r="AE1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>43922</v>
+      </c>
+      <c r="B2">
+        <v>2138.9006645700001</v>
+      </c>
+      <c r="C2">
+        <v>0.1174060293540956</v>
+      </c>
+      <c r="D2">
+        <v>4833.40990616</v>
+      </c>
+      <c r="E2">
+        <v>3.6674382661831727E-2</v>
+      </c>
+      <c r="F2">
+        <v>1435.3239125</v>
+      </c>
+      <c r="G2">
+        <v>3.6710352026549972E-2</v>
+      </c>
+      <c r="H2">
+        <v>14089.046786409999</v>
+      </c>
+      <c r="I2">
+        <v>7.9516869480526817E-2</v>
+      </c>
+      <c r="J2">
+        <v>22496.681269640001</v>
+      </c>
+      <c r="K2">
+        <v>7.1183401675834201E-2</v>
+      </c>
+      <c r="L2">
+        <v>0.25</v>
+      </c>
+      <c r="M2">
+        <v>104.571783804586</v>
+      </c>
+      <c r="N2">
+        <v>7.6680472678778022</v>
+      </c>
+      <c r="O2">
+        <v>-9.5515514698396586E-3</v>
+      </c>
+      <c r="P2">
+        <v>8.4833074822688559</v>
+      </c>
+      <c r="Q2">
+        <v>-2.52416277372749E-2</v>
+      </c>
+      <c r="R2">
+        <v>7.2691458257186348</v>
+      </c>
+      <c r="S2">
+        <v>-5.4684485960745377E-3</v>
+      </c>
+      <c r="T2">
+        <v>9.5531529508235451</v>
+      </c>
+      <c r="U2">
+        <v>-1.55813642880922E-2</v>
+      </c>
+      <c r="V2">
+        <v>10.02112307818633</v>
+      </c>
+      <c r="W2">
+        <v>-1.645301265914334E-2</v>
+      </c>
+      <c r="X2">
+        <v>4.6344532220542991</v>
+      </c>
+      <c r="Y2">
+        <v>-0.29060239695060641</v>
+      </c>
+      <c r="Z2">
+        <v>-9.5527198978147959E-3</v>
+      </c>
+      <c r="AA2">
+        <v>4.1730481972425398E-4</v>
+      </c>
+      <c r="AB2">
+        <v>1.558668939265144E-3</v>
+      </c>
+      <c r="AC2">
+        <v>4.6447869879040482E-4</v>
+      </c>
+      <c r="AD2">
+        <v>-3.4635222137319183E-4</v>
+      </c>
+      <c r="AE2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>43952</v>
+      </c>
+      <c r="B3">
+        <v>2183.1003610900002</v>
+      </c>
+      <c r="C3">
+        <v>0.1124785327905852</v>
+      </c>
+      <c r="D3">
+        <v>4733.6882485699998</v>
+      </c>
+      <c r="E3">
+        <v>3.7745282498055449E-2</v>
+      </c>
+      <c r="F3">
+        <v>1428.6810697999999</v>
+      </c>
+      <c r="G3">
+        <v>3.6032640088950393E-2</v>
+      </c>
+      <c r="H3">
+        <v>14087.11798673</v>
+      </c>
+      <c r="I3">
+        <v>7.8700272163145985E-2</v>
+      </c>
+      <c r="J3">
+        <v>22432.58766619</v>
+      </c>
+      <c r="K3">
+        <v>7.0627852643051409E-2</v>
+      </c>
+      <c r="L3">
+        <v>0.25</v>
+      </c>
+      <c r="M3">
+        <v>116.20409231795</v>
+      </c>
+      <c r="N3">
+        <v>7.6885013294235467</v>
+      </c>
+      <c r="O3">
+        <v>2.045406154574447E-2</v>
+      </c>
+      <c r="P3">
+        <v>8.4624599342024798</v>
+      </c>
+      <c r="Q3">
+        <v>-2.084754806637612E-2</v>
+      </c>
+      <c r="R3">
+        <v>7.2645069688358266</v>
+      </c>
+      <c r="S3">
+        <v>-4.6388568828081844E-3</v>
+      </c>
+      <c r="T3">
+        <v>9.5530160408005855</v>
+      </c>
+      <c r="U3">
+        <v>-1.369100229595688E-4</v>
+      </c>
+      <c r="V3">
+        <v>10.018269987163681</v>
+      </c>
+      <c r="W3">
+        <v>-2.853091022650744E-3</v>
+      </c>
+      <c r="X3">
+        <v>4.7711480763772691</v>
+      </c>
+      <c r="Y3">
+        <v>0.13669485432296999</v>
+      </c>
+      <c r="Z3">
+        <v>-4.9274965635103954E-3</v>
+      </c>
+      <c r="AA3">
+        <v>1.0708998362237219E-3</v>
+      </c>
+      <c r="AB3">
+        <v>-6.7771193759957882E-4</v>
+      </c>
+      <c r="AC3">
+        <v>-8.1659731738083219E-4</v>
+      </c>
+      <c r="AD3">
+        <v>-5.5554903278279277E-4</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>43983</v>
+      </c>
+      <c r="B4">
+        <v>2204.0703212399999</v>
+      </c>
+      <c r="C4">
+        <v>0.11094637160779269</v>
+      </c>
+      <c r="D4">
+        <v>4646.4947893199997</v>
+      </c>
+      <c r="E4">
+        <v>3.8160728975217321E-2</v>
+      </c>
+      <c r="F4">
+        <v>1420.3440982899999</v>
+      </c>
+      <c r="G4">
+        <v>3.7407814911870563E-2</v>
+      </c>
+      <c r="H4">
+        <v>14248.5252177</v>
+      </c>
+      <c r="I4">
+        <v>7.7194744944105012E-2</v>
+      </c>
+      <c r="J4">
+        <v>22519.43442655</v>
+      </c>
+      <c r="K4">
+        <v>6.9934725827005356E-2</v>
+      </c>
+      <c r="L4">
+        <v>0.25</v>
+      </c>
+      <c r="M4">
+        <v>139.91102445364899</v>
+      </c>
+      <c r="N4">
+        <v>7.6980610759525607</v>
+      </c>
+      <c r="O4">
+        <v>9.5597465290140349E-3</v>
+      </c>
+      <c r="P4">
+        <v>8.4438684055763407</v>
+      </c>
+      <c r="Q4">
+        <v>-1.8591528626139109E-2</v>
+      </c>
+      <c r="R4">
+        <v>7.2586544439793306</v>
+      </c>
+      <c r="S4">
+        <v>-5.8525248564960108E-3</v>
+      </c>
+      <c r="T4">
+        <v>9.5644086868462388</v>
+      </c>
+      <c r="U4">
+        <v>1.139264604565327E-2</v>
+      </c>
+      <c r="V4">
+        <v>10.02213396766428</v>
+      </c>
+      <c r="W4">
+        <v>3.863980500595332E-3</v>
+      </c>
+      <c r="X4">
+        <v>4.9373683015533629</v>
+      </c>
+      <c r="Y4">
+        <v>0.16622022517609381</v>
+      </c>
+      <c r="Z4">
+        <v>-1.532161182792507E-3</v>
+      </c>
+      <c r="AA4">
+        <v>4.1544647716187239E-4</v>
+      </c>
+      <c r="AB4">
+        <v>1.3751748229201689E-3</v>
+      </c>
+      <c r="AC4">
+        <v>-1.505527219040972E-3</v>
+      </c>
+      <c r="AD4">
+        <v>-6.9312681604605242E-4</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>44013</v>
+      </c>
+      <c r="B5">
+        <v>2217.3487439099999</v>
+      </c>
+      <c r="C5">
+        <v>0.1156340769146989</v>
+      </c>
+      <c r="D5">
+        <v>4608.5607300699994</v>
+      </c>
+      <c r="E5">
+        <v>3.4936834461017169E-2</v>
+      </c>
+      <c r="F5">
+        <v>1409.0320153600001</v>
+      </c>
+      <c r="G5">
+        <v>3.6914573482356793E-2</v>
+      </c>
+      <c r="H5">
+        <v>14932.27259633</v>
+      </c>
+      <c r="I5">
+        <v>6.9971061896284548E-2</v>
+      </c>
+      <c r="J5">
+        <v>23167.214085669999</v>
+      </c>
+      <c r="K5">
+        <v>6.5361781476635739E-2</v>
+      </c>
+      <c r="L5">
+        <v>0.25</v>
+      </c>
+      <c r="M5">
+        <v>152.544198892754</v>
+      </c>
+      <c r="N5">
+        <v>7.7040675016701661</v>
+      </c>
+      <c r="O5">
+        <v>6.0064257176053459E-3</v>
+      </c>
+      <c r="P5">
+        <v>8.4356708811856684</v>
+      </c>
+      <c r="Q5">
+        <v>-8.1975243906722284E-3</v>
+      </c>
+      <c r="R5">
+        <v>7.2506582336845424</v>
+      </c>
+      <c r="S5">
+        <v>-7.9962102947890301E-3</v>
+      </c>
+      <c r="T5">
+        <v>9.6112800957163511</v>
+      </c>
+      <c r="U5">
+        <v>4.6871408870112319E-2</v>
+      </c>
+      <c r="V5">
+        <v>10.050493372202871</v>
+      </c>
+      <c r="W5">
+        <v>2.8359404538585761E-2</v>
+      </c>
+      <c r="X5">
+        <v>5.0367090662676031</v>
+      </c>
+      <c r="Y5">
+        <v>9.9340764714240137E-2</v>
+      </c>
+      <c r="Z5">
+        <v>4.6877053069062091E-3</v>
+      </c>
+      <c r="AA5">
+        <v>-3.2238945142001531E-3</v>
+      </c>
+      <c r="AB5">
+        <v>-4.932414295137702E-4</v>
+      </c>
+      <c r="AC5">
+        <v>-7.2236830478204636E-3</v>
+      </c>
+      <c r="AD5">
+        <v>-4.5729443503696177E-3</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>44044</v>
+      </c>
+      <c r="B6">
+        <v>2261.7211269300001</v>
+      </c>
+      <c r="C6">
+        <v>0.11143274656150851</v>
+      </c>
+      <c r="D6">
+        <v>4619.2933561999998</v>
+      </c>
+      <c r="E6">
+        <v>3.2603356746732523E-2</v>
+      </c>
+      <c r="F6">
+        <v>1401.97957561</v>
+      </c>
+      <c r="G6">
+        <v>3.6528284449306427E-2</v>
+      </c>
+      <c r="H6">
+        <v>15448.824612799999</v>
+      </c>
+      <c r="I6">
+        <v>6.5903823177358822E-2</v>
+      </c>
+      <c r="J6">
+        <v>23731.818671540001</v>
+      </c>
+      <c r="K6">
+        <v>6.2025704857388432E-2</v>
+      </c>
+      <c r="L6">
+        <v>0.25</v>
+      </c>
+      <c r="M6">
+        <v>156.36406569440399</v>
+      </c>
+      <c r="N6">
+        <v>7.7238813630147067</v>
+      </c>
+      <c r="O6">
+        <v>1.9813861344540658E-2</v>
+      </c>
+      <c r="P6">
+        <v>8.4379970191737872</v>
+      </c>
+      <c r="Q6">
+        <v>2.3261379881187589E-3</v>
+      </c>
+      <c r="R6">
+        <v>7.2456404994499044</v>
+      </c>
+      <c r="S6">
+        <v>-5.017734234637139E-3</v>
+      </c>
+      <c r="T6">
+        <v>9.6452882025904785</v>
+      </c>
+      <c r="U6">
+        <v>3.4008106874127357E-2</v>
+      </c>
+      <c r="V6">
+        <v>10.07457198667599</v>
+      </c>
+      <c r="W6">
+        <v>2.4078614473125981E-2</v>
+      </c>
+      <c r="X6">
+        <v>5.0542680547098611</v>
+      </c>
+      <c r="Y6">
+        <v>1.7558988442258009E-2</v>
+      </c>
+      <c r="Z6">
+        <v>-4.2013303531903967E-3</v>
+      </c>
+      <c r="AA6">
+        <v>-2.3334777142846458E-3</v>
+      </c>
+      <c r="AB6">
+        <v>-3.8628903305036599E-4</v>
+      </c>
+      <c r="AC6">
+        <v>-4.0672387189257253E-3</v>
+      </c>
+      <c r="AD6">
+        <v>-3.336076619247307E-3</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>44075</v>
+      </c>
+      <c r="B7">
+        <v>2276.9921576400002</v>
+      </c>
+      <c r="C7">
+        <v>0.11070809773946309</v>
+      </c>
+      <c r="D7">
+        <v>4673.3158472900004</v>
+      </c>
+      <c r="E7">
+        <v>3.0915695022792341E-2</v>
+      </c>
+      <c r="F7">
+        <v>1403.2395340800001</v>
+      </c>
+      <c r="G7">
+        <v>4.1048794386886259E-2</v>
+      </c>
+      <c r="H7">
+        <v>16164.727005320001</v>
+      </c>
+      <c r="I7">
+        <v>6.2153965633279233E-2</v>
+      </c>
+      <c r="J7">
+        <v>24518.274544330001</v>
+      </c>
+      <c r="K7">
+        <v>5.9501065340153432E-2</v>
+      </c>
+      <c r="L7">
+        <v>0.25</v>
+      </c>
+      <c r="M7">
+        <v>160.26131398211101</v>
+      </c>
+      <c r="N7">
+        <v>7.7306106218944359</v>
+      </c>
+      <c r="O7">
+        <v>6.7292588797291941E-3</v>
+      </c>
+      <c r="P7">
+        <v>8.4496241302494202</v>
+      </c>
+      <c r="Q7">
+        <v>1.1627111075632969E-2</v>
+      </c>
+      <c r="R7">
+        <v>7.2465387954513636</v>
+      </c>
+      <c r="S7">
+        <v>8.9829600145918675E-4</v>
+      </c>
+      <c r="T7">
+        <v>9.6905868020070312</v>
+      </c>
+      <c r="U7">
+        <v>4.5298599416552683E-2</v>
+      </c>
+      <c r="V7">
+        <v>10.10717401825641</v>
+      </c>
+      <c r="W7">
+        <v>3.2602031580420743E-2</v>
+      </c>
+      <c r="X7">
+        <v>5.0882121949345764</v>
+      </c>
+      <c r="Y7">
+        <v>3.3944140224715369E-2</v>
+      </c>
+      <c r="Z7">
+        <v>-7.2464882204541226E-4</v>
+      </c>
+      <c r="AA7">
+        <v>-1.6876617239401819E-3</v>
+      </c>
+      <c r="AB7">
+        <v>4.5205099375798322E-3</v>
+      </c>
+      <c r="AC7">
+        <v>-3.7498575440795892E-3</v>
+      </c>
+      <c r="AD7">
+        <v>-2.524639517235E-3</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>44105</v>
+      </c>
+      <c r="B8">
+        <v>2231.4262205499999</v>
+      </c>
+      <c r="C8">
+        <v>0.10771210436917709</v>
+      </c>
+      <c r="D8">
+        <v>4806.8549881299996</v>
+      </c>
+      <c r="E8">
+        <v>3.1291336042262183E-2</v>
+      </c>
+      <c r="F8">
+        <v>1404.1004755700001</v>
+      </c>
+      <c r="G8">
+        <v>4.3559165860385649E-2</v>
+      </c>
+      <c r="H8">
+        <v>16643.936121160001</v>
+      </c>
+      <c r="I8">
+        <v>5.7584737024525517E-2</v>
+      </c>
+      <c r="J8">
+        <v>25086.317805409999</v>
+      </c>
+      <c r="K8">
+        <v>5.6220393512109917E-2</v>
+      </c>
+      <c r="L8">
+        <v>0.25</v>
+      </c>
+      <c r="M8">
+        <v>166.74684518517901</v>
+      </c>
+      <c r="N8">
+        <v>7.7103962208070786</v>
+      </c>
+      <c r="O8">
+        <v>-2.0214401087357281E-2</v>
+      </c>
+      <c r="P8">
+        <v>8.4777983006259525</v>
+      </c>
+      <c r="Q8">
+        <v>2.8174170376532359E-2</v>
+      </c>
+      <c r="R8">
+        <v>7.2471521458214863</v>
+      </c>
+      <c r="S8">
+        <v>6.1335037012266724E-4</v>
+      </c>
+      <c r="T8">
+        <v>9.7198012321454552</v>
+      </c>
+      <c r="U8">
+        <v>2.921443013842406E-2</v>
+      </c>
+      <c r="V8">
+        <v>10.130077869140671</v>
+      </c>
+      <c r="W8">
+        <v>2.2903850884253171E-2</v>
+      </c>
+      <c r="X8">
+        <v>5.1376596451039553</v>
+      </c>
+      <c r="Y8">
+        <v>4.9447450169378897E-2</v>
+      </c>
+      <c r="Z8">
+        <v>-2.9959933702859991E-3</v>
+      </c>
+      <c r="AA8">
+        <v>3.7564101946984188E-4</v>
+      </c>
+      <c r="AB8">
+        <v>2.5103714734993898E-3</v>
+      </c>
+      <c r="AC8">
+        <v>-4.5692286087537157E-3</v>
+      </c>
+      <c r="AD8">
+        <v>-3.280671828043515E-3</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>44136</v>
+      </c>
+      <c r="B9">
+        <v>2280.1507402299999</v>
+      </c>
+      <c r="C9">
+        <v>0.10319941129693209</v>
+      </c>
+      <c r="D9">
+        <v>4948.6570592999997</v>
+      </c>
+      <c r="E9">
+        <v>3.0511784985431639E-2</v>
+      </c>
+      <c r="F9">
+        <v>1409.1993044200001</v>
+      </c>
+      <c r="G9">
+        <v>4.370211886766949E-2</v>
+      </c>
+      <c r="H9">
+        <v>17039.103716760001</v>
+      </c>
+      <c r="I9">
+        <v>5.4603099088178682E-2</v>
+      </c>
+      <c r="J9">
+        <v>25677.110820710001</v>
+      </c>
+      <c r="K9">
+        <v>5.3677200989386442E-2</v>
+      </c>
+      <c r="L9">
+        <v>0.25</v>
+      </c>
+      <c r="M9">
+        <v>168.292170423214</v>
+      </c>
+      <c r="N9">
+        <v>7.7319968338990082</v>
+      </c>
+      <c r="O9">
+        <v>2.160061309192951E-2</v>
+      </c>
+      <c r="P9">
+        <v>8.5068715176024057</v>
+      </c>
+      <c r="Q9">
+        <v>2.907321697645315E-2</v>
+      </c>
+      <c r="R9">
+        <v>7.2507769528677546</v>
+      </c>
+      <c r="S9">
+        <v>3.6248070462692179E-3</v>
+      </c>
+      <c r="T9">
+        <v>9.7432662002182528</v>
+      </c>
+      <c r="U9">
+        <v>2.3464968072797628E-2</v>
+      </c>
+      <c r="V9">
+        <v>10.153355244492809</v>
+      </c>
+      <c r="W9">
+        <v>2.327737535214958E-2</v>
+      </c>
+      <c r="X9">
+        <v>5.1373730790035861</v>
+      </c>
+      <c r="Y9">
+        <v>-2.8656610036925661E-4</v>
+      </c>
+      <c r="Z9">
+        <v>-4.5126930722449998E-3</v>
+      </c>
+      <c r="AA9">
+        <v>-7.795510568305436E-4</v>
+      </c>
+      <c r="AB9">
+        <v>1.4295300728384139E-4</v>
+      </c>
+      <c r="AC9">
+        <v>-2.9816379363468361E-3</v>
+      </c>
+      <c r="AD9">
+        <v>-2.5431925227234749E-3</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>44166</v>
+      </c>
+      <c r="B10">
+        <v>2300.3196402100002</v>
+      </c>
+      <c r="C10">
+        <v>0.101678955690109</v>
+      </c>
+      <c r="D10">
+        <v>5069.7182674599999</v>
+      </c>
+      <c r="E10">
+        <v>2.6994189913548239E-2</v>
+      </c>
+      <c r="F10">
+        <v>1416.1758750700001</v>
+      </c>
+      <c r="G10">
+        <v>4.279667385027601E-2</v>
+      </c>
+      <c r="H10">
+        <v>17303.47789563</v>
+      </c>
+      <c r="I10">
+        <v>4.9784130401181181E-2</v>
+      </c>
+      <c r="J10">
+        <v>26089.69167837</v>
+      </c>
+      <c r="K10">
+        <v>4.9551879317600647E-2</v>
+      </c>
+      <c r="L10">
+        <v>0.25</v>
+      </c>
+      <c r="M10">
+        <v>172.400120770981</v>
+      </c>
+      <c r="N10">
+        <v>7.7408033662655971</v>
+      </c>
+      <c r="O10">
+        <v>8.8065323665889039E-3</v>
+      </c>
+      <c r="P10">
+        <v>8.5310405264929159</v>
+      </c>
+      <c r="Q10">
+        <v>2.4169008890510209E-2</v>
+      </c>
+      <c r="R10">
+        <v>7.2557154720987027</v>
+      </c>
+      <c r="S10">
+        <v>4.9385192309472359E-3</v>
+      </c>
+      <c r="T10">
+        <v>9.7586627947106361</v>
+      </c>
+      <c r="U10">
+        <v>1.539659449238329E-2</v>
+      </c>
+      <c r="V10">
+        <v>10.16929556044385</v>
+      </c>
+      <c r="W10">
+        <v>1.594031595103651E-2</v>
+      </c>
+      <c r="X10">
+        <v>5.2531473915789588</v>
+      </c>
+      <c r="Y10">
+        <v>0.1157743125753727</v>
+      </c>
+      <c r="Z10">
+        <v>-1.5204556068230961E-3</v>
+      </c>
+      <c r="AA10">
+        <v>-3.5175950718833999E-3</v>
+      </c>
+      <c r="AB10">
+        <v>-9.0544501739348027E-4</v>
+      </c>
+      <c r="AC10">
+        <v>-4.8189686869975004E-3</v>
+      </c>
+      <c r="AD10">
+        <v>-4.1253216717857949E-3</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>44197</v>
+      </c>
+      <c r="B11">
+        <v>2275.7306163899998</v>
+      </c>
+      <c r="C11">
+        <v>0.1052414975766867</v>
+      </c>
+      <c r="D11">
+        <v>5112.7377065800001</v>
+      </c>
+      <c r="E11">
+        <v>2.6677292383777761E-2</v>
+      </c>
+      <c r="F11">
+        <v>1409.5821437</v>
+      </c>
+      <c r="G11">
+        <v>4.2525803819176179E-2</v>
+      </c>
+      <c r="H11">
+        <v>17303.545139239999</v>
+      </c>
+      <c r="I11">
+        <v>5.1406725220879752E-2</v>
+      </c>
+      <c r="J11">
+        <v>26101.595605909999</v>
+      </c>
+      <c r="K11">
+        <v>5.0776876665727999E-2</v>
+      </c>
+      <c r="L11">
+        <v>0.25</v>
+      </c>
+      <c r="M11">
+        <v>172.90099314200501</v>
+      </c>
+      <c r="N11">
+        <v>7.730056429888946</v>
+      </c>
+      <c r="O11">
+        <v>-1.074693637665103E-2</v>
+      </c>
+      <c r="P11">
+        <v>8.5394902944447626</v>
+      </c>
+      <c r="Q11">
+        <v>8.4497679518467095E-3</v>
+      </c>
+      <c r="R11">
+        <v>7.2510485874654709</v>
+      </c>
+      <c r="S11">
+        <v>-4.6668846332318381E-3</v>
+      </c>
+      <c r="T11">
+        <v>9.758666680835713</v>
+      </c>
+      <c r="U11">
+        <v>3.8861250768462696E-6</v>
+      </c>
+      <c r="V11">
+        <v>10.16975172576821</v>
+      </c>
+      <c r="W11">
+        <v>4.5616532436021368E-4</v>
+      </c>
+      <c r="X11">
+        <v>5.0818272569195218</v>
+      </c>
+      <c r="Y11">
+        <v>-0.1713201346594371</v>
+      </c>
+      <c r="Z11">
+        <v>3.562541886577703E-3</v>
+      </c>
+      <c r="AA11">
+        <v>-3.168975297704775E-4</v>
+      </c>
+      <c r="AB11">
+        <v>-2.7087003109983049E-4</v>
+      </c>
+      <c r="AC11">
+        <v>1.6225948196985709E-3</v>
+      </c>
+      <c r="AD11">
+        <v>1.2249973481273521E-3</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>44228</v>
+      </c>
+      <c r="B12">
+        <v>2279.78727114</v>
+      </c>
+      <c r="C12">
+        <v>0.1030168990515333</v>
+      </c>
+      <c r="D12">
+        <v>5152.0684472299999</v>
+      </c>
+      <c r="E12">
+        <v>2.6486224526649459E-2</v>
+      </c>
+      <c r="F12">
+        <v>1410.2242385100001</v>
+      </c>
+      <c r="G12">
+        <v>4.2750860993354352E-2</v>
+      </c>
+      <c r="H12">
+        <v>17292.186950200001</v>
+      </c>
+      <c r="I12">
+        <v>5.8556908493768538E-2</v>
+      </c>
+      <c r="J12">
+        <v>26134.26690708</v>
+      </c>
+      <c r="K12">
+        <v>5.5260045030716312E-2</v>
+      </c>
+      <c r="L12">
+        <v>0.25</v>
+      </c>
+      <c r="M12">
+        <v>169.15538756642201</v>
+      </c>
+      <c r="N12">
+        <v>7.7318374154639926</v>
+      </c>
+      <c r="O12">
+        <v>1.7809855750465791E-3</v>
+      </c>
+      <c r="P12">
+        <v>8.5471535532607668</v>
+      </c>
+      <c r="Q12">
+        <v>7.6632588160041593E-3</v>
+      </c>
+      <c r="R12">
+        <v>7.2515040051318387</v>
+      </c>
+      <c r="S12">
+        <v>4.5541766636780778E-4</v>
+      </c>
+      <c r="T12">
+        <v>9.7580100570984989</v>
+      </c>
+      <c r="U12">
+        <v>-6.566237372140904E-4</v>
+      </c>
+      <c r="V12">
+        <v>10.17100264051752</v>
+      </c>
+      <c r="W12">
+        <v>1.250914749313381E-3</v>
+      </c>
+      <c r="X12">
+        <v>5.0485044532861796</v>
+      </c>
+      <c r="Y12">
+        <v>-3.3322803633342168E-2</v>
+      </c>
+      <c r="Z12">
+        <v>-2.2245985251534012E-3</v>
+      </c>
+      <c r="AA12">
+        <v>-1.9106785712830199E-4</v>
+      </c>
+      <c r="AB12">
+        <v>2.2505717417817259E-4</v>
+      </c>
+      <c r="AC12">
+        <v>7.1501832728887854E-3</v>
+      </c>
+      <c r="AD12">
+        <v>4.4831683649883131E-3</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>44256</v>
+      </c>
+      <c r="B13">
+        <v>2271.0733725499999</v>
+      </c>
+      <c r="C13">
+        <v>9.826505070570403E-2</v>
+      </c>
+      <c r="D13">
+        <v>5229.7713057399997</v>
+      </c>
+      <c r="E13">
+        <v>2.6958617246849309E-2</v>
+      </c>
+      <c r="F13">
+        <v>1410.99503755</v>
+      </c>
+      <c r="G13">
+        <v>4.2955943746791667E-2</v>
+      </c>
+      <c r="H13">
+        <v>17410.84239396</v>
+      </c>
+      <c r="I13">
+        <v>6.3918540870605292E-2</v>
+      </c>
+      <c r="J13">
+        <v>26322.6821098</v>
+      </c>
+      <c r="K13">
+        <v>5.8415050610193427E-2</v>
+      </c>
+      <c r="L13">
+        <v>0.25</v>
+      </c>
+      <c r="M13">
+        <v>168.75683535705301</v>
+      </c>
+      <c r="N13">
+        <v>7.7280078500600933</v>
+      </c>
+      <c r="O13">
+        <v>-3.8295654038993381E-3</v>
+      </c>
+      <c r="P13">
+        <v>8.5621228287109297</v>
+      </c>
+      <c r="Q13">
+        <v>1.4969275450162909E-2</v>
+      </c>
+      <c r="R13">
+        <v>7.2520504348728521</v>
+      </c>
+      <c r="S13">
+        <v>5.4642974101337671E-4</v>
+      </c>
+      <c r="T13">
+        <v>9.7648484172298264</v>
+      </c>
+      <c r="U13">
+        <v>6.8383601313275477E-3</v>
+      </c>
+      <c r="V13">
+        <v>10.17818628411519</v>
+      </c>
+      <c r="W13">
+        <v>7.1836435976635471E-3</v>
+      </c>
+      <c r="X13">
+        <v>5.1063229783943678</v>
+      </c>
+      <c r="Y13">
+        <v>5.781852510818819E-2</v>
+      </c>
+      <c r="Z13">
+        <v>-4.751848345829271E-3</v>
+      </c>
+      <c r="AA13">
+        <v>4.7239272019984971E-4</v>
+      </c>
+      <c r="AB13">
+        <v>2.050827534373148E-4</v>
+      </c>
+      <c r="AC13">
+        <v>5.3616323768367544E-3</v>
+      </c>
+      <c r="AD13">
+        <v>3.155005579477115E-3</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>44287</v>
+      </c>
+      <c r="B14">
+        <v>2280.2364451200001</v>
+      </c>
+      <c r="C14">
+        <v>9.9853541937409723E-2</v>
+      </c>
+      <c r="D14">
+        <v>5299.7645609700003</v>
+      </c>
+      <c r="E14">
+        <v>2.8025877446302049E-2</v>
+      </c>
+      <c r="F14">
+        <v>1414.0914274300001</v>
+      </c>
+      <c r="G14">
+        <v>4.3759021969647802E-2</v>
+      </c>
+      <c r="H14">
+        <v>17590.599337340002</v>
+      </c>
+      <c r="I14">
+        <v>6.6101338952208197E-2</v>
+      </c>
+      <c r="J14">
+        <v>26584.691770860001</v>
+      </c>
+      <c r="K14">
+        <v>6.0217424312766929E-2</v>
+      </c>
+      <c r="L14">
+        <v>0.25</v>
+      </c>
+      <c r="M14">
+        <v>167.832160638837</v>
+      </c>
+      <c r="N14">
+        <v>7.7320344205715994</v>
+      </c>
+      <c r="O14">
+        <v>4.0265705115052342E-3</v>
+      </c>
+      <c r="P14">
+        <v>8.5754176760950163</v>
+      </c>
+      <c r="Q14">
+        <v>1.3294847384086589E-2</v>
+      </c>
+      <c r="R14">
+        <v>7.2542425030861768</v>
+      </c>
+      <c r="S14">
+        <v>2.1920682133247378E-3</v>
+      </c>
+      <c r="T14">
+        <v>9.7751199097685415</v>
+      </c>
+      <c r="U14">
+        <v>1.0271492538715069E-2</v>
+      </c>
+      <c r="V14">
+        <v>10.18809083177155</v>
+      </c>
+      <c r="W14">
+        <v>9.9045476563581758E-3</v>
+      </c>
+      <c r="X14">
+        <v>5.1038408364617132</v>
+      </c>
+      <c r="Y14">
+        <v>-2.482141932654613E-3</v>
+      </c>
+      <c r="Z14">
+        <v>1.5884912317056939E-3</v>
+      </c>
+      <c r="AA14">
+        <v>1.067260199452739E-3</v>
+      </c>
+      <c r="AB14">
+        <v>8.0307822285613506E-4</v>
+      </c>
+      <c r="AC14">
+        <v>2.1827980816029051E-3</v>
+      </c>
+      <c r="AD14">
+        <v>1.8023737025735021E-3</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>44317</v>
+      </c>
+      <c r="B15">
+        <v>2276.4251643399998</v>
+      </c>
+      <c r="C15">
+        <v>9.7517738785127928E-2</v>
+      </c>
+      <c r="D15">
+        <v>5333.5101946000004</v>
+      </c>
+      <c r="E15">
+        <v>3.2891037969255521E-2</v>
+      </c>
+      <c r="F15">
+        <v>1414.1026799700001</v>
+      </c>
+      <c r="G15">
+        <v>4.5129050290289997E-2</v>
+      </c>
+      <c r="H15">
+        <v>17861.444640760001</v>
+      </c>
+      <c r="I15">
+        <v>6.6689788999582042E-2</v>
+      </c>
+      <c r="J15">
+        <v>26885.48267967</v>
+      </c>
+      <c r="K15">
+        <v>6.1461035527158411E-2</v>
+      </c>
+      <c r="L15">
+        <v>0.25</v>
+      </c>
+      <c r="M15">
+        <v>172.46262082341099</v>
+      </c>
+      <c r="N15">
+        <v>7.7303615811134847</v>
+      </c>
+      <c r="O15">
+        <v>-1.672839458113806E-3</v>
+      </c>
+      <c r="P15">
+        <v>8.581764873491478</v>
+      </c>
+      <c r="Q15">
+        <v>6.3471973964617234E-3</v>
+      </c>
+      <c r="R15">
+        <v>7.2542504604890796</v>
+      </c>
+      <c r="S15">
+        <v>7.9574029028250948E-6</v>
+      </c>
+      <c r="T15">
+        <v>9.7903997380999677</v>
+      </c>
+      <c r="U15">
+        <v>1.527982833142616E-2</v>
+      </c>
+      <c r="V15">
+        <v>10.19934174257601</v>
+      </c>
+      <c r="W15">
+        <v>1.125091080446694E-2</v>
+      </c>
+      <c r="X15">
+        <v>5.1672691739430272</v>
+      </c>
+      <c r="Y15">
+        <v>6.3428337481314045E-2</v>
+      </c>
+      <c r="Z15">
+        <v>-2.3358031522817961E-3</v>
+      </c>
+      <c r="AA15">
+        <v>4.8651605229534734E-3</v>
+      </c>
+      <c r="AB15">
+        <v>1.3700283206421961E-3</v>
+      </c>
+      <c r="AC15">
+        <v>5.8845004737384521E-4</v>
+      </c>
+      <c r="AD15">
+        <v>1.2436112143914819E-3</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>44348</v>
+      </c>
+      <c r="B16">
+        <v>2286.9315393799998</v>
+      </c>
+      <c r="C16">
+        <v>9.1658109978590793E-2</v>
+      </c>
+      <c r="D16">
+        <v>5358.6517146100005</v>
+      </c>
+      <c r="E16">
+        <v>3.1368390944630307E-2</v>
+      </c>
+      <c r="F16">
+        <v>1408.03971073</v>
+      </c>
+      <c r="G16">
+        <v>4.4266246424034192E-2</v>
+      </c>
+      <c r="H16">
+        <v>18024.676300989999</v>
+      </c>
+      <c r="I16">
+        <v>6.267882312027695E-2</v>
+      </c>
+      <c r="J16">
+        <v>27078.29926571</v>
+      </c>
+      <c r="K16">
+        <v>5.7972704250960252E-2</v>
+      </c>
+      <c r="L16">
+        <v>0.25</v>
+      </c>
+      <c r="M16">
+        <v>172.756272866323</v>
+      </c>
+      <c r="N16">
+        <v>7.7349662588917383</v>
+      </c>
+      <c r="O16">
+        <v>4.6046777782535742E-3</v>
+      </c>
+      <c r="P16">
+        <v>8.5864676766401846</v>
+      </c>
+      <c r="Q16">
+        <v>4.7028031487066357E-3</v>
+      </c>
+      <c r="R16">
+        <v>7.2499537399637379</v>
+      </c>
+      <c r="S16">
+        <v>-4.2967205253416907E-3</v>
+      </c>
+      <c r="T16">
+        <v>9.7994970036556968</v>
+      </c>
+      <c r="U16">
+        <v>9.0972655557290949E-3</v>
+      </c>
+      <c r="V16">
+        <v>10.20648792098121</v>
+      </c>
+      <c r="W16">
+        <v>7.1461784051916064E-3</v>
+      </c>
+      <c r="X16">
+        <v>5.1477490955581402</v>
+      </c>
+      <c r="Y16">
+        <v>-1.9520078384887011E-2</v>
+      </c>
+      <c r="Z16">
+        <v>-5.8596288065371344E-3</v>
+      </c>
+      <c r="AA16">
+        <v>-1.522647024625214E-3</v>
+      </c>
+      <c r="AB16">
+        <v>-8.6280386625580546E-4</v>
+      </c>
+      <c r="AC16">
+        <v>-4.0109658793050923E-3</v>
+      </c>
+      <c r="AD16">
+        <v>-3.4883312761981589E-3</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>44378</v>
+      </c>
+      <c r="B17">
+        <v>2262.2419197999998</v>
+      </c>
+      <c r="C17">
+        <v>9.8105483802378254E-2</v>
+      </c>
+      <c r="D17">
+        <v>5368.7611469200001</v>
+      </c>
+      <c r="E17">
+        <v>3.2271793767431257E-2</v>
+      </c>
+      <c r="F17">
+        <v>1409.3347980000001</v>
+      </c>
+      <c r="G17">
+        <v>4.3749786947359537E-2</v>
+      </c>
+      <c r="H17">
+        <v>18214.69351021</v>
+      </c>
+      <c r="I17">
+        <v>6.5127595126157206E-2</v>
+      </c>
+      <c r="J17">
+        <v>27255.03137493</v>
+      </c>
+      <c r="K17">
+        <v>6.0287407098030543E-2</v>
+      </c>
+      <c r="L17">
+        <v>0.25</v>
+      </c>
+      <c r="M17">
+        <v>173.54042175974399</v>
+      </c>
+      <c r="N17">
+        <v>7.7241116004710788</v>
+      </c>
+      <c r="O17">
+        <v>-1.085465842065947E-2</v>
+      </c>
+      <c r="P17">
+        <v>8.5883524619902474</v>
+      </c>
+      <c r="Q17">
+        <v>1.8847853500627561E-3</v>
+      </c>
+      <c r="R17">
+        <v>7.2508730975835407</v>
+      </c>
+      <c r="S17">
+        <v>9.193576198027742E-4</v>
+      </c>
+      <c r="T17">
+        <v>9.8099838830705224</v>
+      </c>
+      <c r="U17">
+        <v>1.0486879414825619E-2</v>
+      </c>
+      <c r="V17">
+        <v>10.212993420660069</v>
+      </c>
+      <c r="W17">
+        <v>6.5054996788695973E-3</v>
+      </c>
+      <c r="X17">
+        <v>5.1617476485985376</v>
+      </c>
+      <c r="Y17">
+        <v>1.3998553040397431E-2</v>
+      </c>
+      <c r="Z17">
+        <v>6.4473738237874612E-3</v>
+      </c>
+      <c r="AA17">
+        <v>9.0340282280094997E-4</v>
+      </c>
+      <c r="AB17">
+        <v>-5.1645947667465497E-4</v>
+      </c>
+      <c r="AC17">
+        <v>2.448772005880256E-3</v>
+      </c>
+      <c r="AD17">
+        <v>2.3147028470702912E-3</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>44409</v>
+      </c>
+      <c r="B18">
+        <v>2234.4294547300001</v>
+      </c>
+      <c r="C18">
+        <v>9.8231403616420049E-2</v>
+      </c>
+      <c r="D18">
+        <v>5406.58861299</v>
+      </c>
+      <c r="E18">
+        <v>3.0962517930030201E-2</v>
+      </c>
+      <c r="F18">
+        <v>1274.8114010700001</v>
+      </c>
+      <c r="G18">
+        <v>3.31111587287116E-2</v>
+      </c>
+      <c r="H18">
+        <v>18427.78186173</v>
+      </c>
+      <c r="I18">
+        <v>6.3027044009135183E-2</v>
+      </c>
+      <c r="J18">
+        <v>27343.611330520002</v>
+      </c>
+      <c r="K18">
+        <v>5.8169047983602687E-2</v>
+      </c>
+      <c r="L18">
+        <v>0.5</v>
+      </c>
+      <c r="M18">
+        <v>174.87920486451901</v>
+      </c>
+      <c r="N18">
+        <v>7.7117411969330876</v>
+      </c>
+      <c r="O18">
+        <v>-1.237040353799035E-2</v>
+      </c>
+      <c r="P18">
+        <v>8.5953736023354335</v>
+      </c>
+      <c r="Q18">
+        <v>7.0211403451860832E-3</v>
+      </c>
+      <c r="R18">
+        <v>7.1505535259217652</v>
+      </c>
+      <c r="S18">
+        <v>-0.10031957166177551</v>
+      </c>
+      <c r="T18">
+        <v>9.8216146886583093</v>
+      </c>
+      <c r="U18">
+        <v>1.163080558778695E-2</v>
+      </c>
+      <c r="V18">
+        <v>10.21623819118618</v>
+      </c>
+      <c r="W18">
+        <v>3.2447705261073878E-3</v>
+      </c>
+      <c r="X18">
+        <v>5.1677028585334774</v>
+      </c>
+      <c r="Y18">
+        <v>5.9552099349398091E-3</v>
+      </c>
+      <c r="Z18">
+        <v>1.2591981404179439E-4</v>
+      </c>
+      <c r="AA18">
+        <v>-1.3092758374010571E-3</v>
+      </c>
+      <c r="AB18">
+        <v>-1.0638628218647941E-2</v>
+      </c>
+      <c r="AC18">
+        <v>-2.1005511170220231E-3</v>
+      </c>
+      <c r="AD18">
+        <v>-2.1183591144278559E-3</v>
+      </c>
+      <c r="AE18">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>44440</v>
+      </c>
+      <c r="B19">
+        <v>2202.2242701199998</v>
+      </c>
+      <c r="C19">
+        <v>0.1005012039976927</v>
+      </c>
+      <c r="D19">
+        <v>5473.4202434999997</v>
+      </c>
+      <c r="E19">
+        <v>3.062295816570073E-2</v>
+      </c>
+      <c r="F19">
+        <v>1277.1083010699999</v>
+      </c>
+      <c r="G19">
+        <v>3.2102560257145203E-2</v>
+      </c>
+      <c r="H19">
+        <v>18797.73941237</v>
+      </c>
+      <c r="I19">
+        <v>6.1177140654117099E-2</v>
+      </c>
+      <c r="J19">
+        <v>27750.49222706</v>
+      </c>
+      <c r="K19">
+        <v>5.6933365038454462E-2</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19">
+        <v>175.854950933071</v>
+      </c>
+      <c r="N19">
+        <v>7.6972231604706369</v>
+      </c>
+      <c r="O19">
+        <v>-1.451803646245153E-2</v>
+      </c>
+      <c r="P19">
+        <v>8.6076589730490269</v>
+      </c>
+      <c r="Q19">
+        <v>1.228537071359348E-2</v>
+      </c>
+      <c r="R19">
+        <v>7.1523536614184504</v>
+      </c>
+      <c r="S19">
+        <v>1.800135496684341E-3</v>
+      </c>
+      <c r="T19">
+        <v>9.8414918975652768</v>
+      </c>
+      <c r="U19">
+        <v>1.9877208906967429E-2</v>
+      </c>
+      <c r="V19">
+        <v>10.231008856929339</v>
+      </c>
+      <c r="W19">
+        <v>1.477066574315522E-2</v>
+      </c>
+      <c r="X19">
+        <v>5.1837894023935513</v>
+      </c>
+      <c r="Y19">
+        <v>1.608654386007391E-2</v>
+      </c>
+      <c r="Z19">
+        <v>2.2698003812726551E-3</v>
+      </c>
+      <c r="AA19">
+        <v>-3.3955976432947088E-4</v>
+      </c>
+      <c r="AB19">
+        <v>-1.008598471566396E-3</v>
+      </c>
+      <c r="AC19">
+        <v>-1.8499033550180839E-3</v>
+      </c>
+      <c r="AD19">
+        <v>-1.235682945148225E-3</v>
+      </c>
+      <c r="AE19">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>44470</v>
+      </c>
+      <c r="B20">
+        <v>2194.2493606399998</v>
+      </c>
+      <c r="C20">
+        <v>0.1004161101114477</v>
+      </c>
+      <c r="D20">
+        <v>5571.17602627</v>
+      </c>
+      <c r="E20">
+        <v>2.930325374753975E-2</v>
+      </c>
+      <c r="F20">
+        <v>1285.5089196199999</v>
+      </c>
+      <c r="G20">
+        <v>3.1440552673837073E-2</v>
+      </c>
+      <c r="H20">
+        <v>19083.164364209999</v>
+      </c>
+      <c r="I20">
+        <v>6.1382550182132331E-2</v>
+      </c>
+      <c r="J20">
+        <v>28134.098670740001</v>
+      </c>
+      <c r="K20">
+        <v>5.6706347481436388E-2</v>
+      </c>
+      <c r="L20">
+        <v>1.5</v>
+      </c>
+      <c r="M20">
+        <v>175.023326475673</v>
+      </c>
+      <c r="N20">
+        <v>7.6935952900924418</v>
+      </c>
+      <c r="O20">
+        <v>-3.6278703781951189E-3</v>
+      </c>
+      <c r="P20">
+        <v>8.6253614464108921</v>
+      </c>
+      <c r="Q20">
+        <v>1.7702473361865149E-2</v>
+      </c>
+      <c r="R20">
+        <v>7.1589099653205341</v>
+      </c>
+      <c r="S20">
+        <v>6.5563039020846148E-3</v>
+      </c>
+      <c r="T20">
+        <v>9.8565617784319723</v>
+      </c>
+      <c r="U20">
+        <v>1.5069880866695581E-2</v>
+      </c>
+      <c r="V20">
+        <v>10.244737595482169</v>
+      </c>
+      <c r="W20">
+        <v>1.372873855283707E-2</v>
+      </c>
+      <c r="X20">
+        <v>5.1842126201835352</v>
+      </c>
+      <c r="Y20">
+        <v>4.2321778998388743E-4</v>
+      </c>
+      <c r="Z20">
+        <v>-8.5093886245002359E-5</v>
+      </c>
+      <c r="AA20">
+        <v>-1.319704418160979E-3</v>
+      </c>
+      <c r="AB20">
+        <v>-6.6200758330813014E-4</v>
+      </c>
+      <c r="AC20">
+        <v>2.0540952801523241E-4</v>
+      </c>
+      <c r="AD20">
+        <v>-2.270175570180735E-4</v>
+      </c>
+      <c r="AE20">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>44501</v>
+      </c>
+      <c r="B21">
+        <v>2172.2655704700001</v>
+      </c>
+      <c r="C21">
+        <v>9.8535122012585449E-2</v>
+      </c>
+      <c r="D21">
+        <v>5670.17393722</v>
+      </c>
+      <c r="E21">
+        <v>2.8580077620943781E-2</v>
+      </c>
+      <c r="F21">
+        <v>1300.8241159700001</v>
+      </c>
+      <c r="G21">
+        <v>3.1301938325180197E-2</v>
+      </c>
+      <c r="H21">
+        <v>19422.658219389999</v>
+      </c>
+      <c r="I21">
+        <v>5.9420327775620327E-2</v>
+      </c>
+      <c r="J21">
+        <v>28565.92184305</v>
+      </c>
+      <c r="K21">
+        <v>5.499271148437309E-2</v>
+      </c>
+      <c r="L21">
+        <v>2</v>
+      </c>
+      <c r="M21">
+        <v>174.28334484974999</v>
+      </c>
+      <c r="N21">
+        <v>7.6835259435932697</v>
+      </c>
+      <c r="O21">
+        <v>-1.0069346499172131E-2</v>
+      </c>
+      <c r="P21">
+        <v>8.6429750730096533</v>
+      </c>
+      <c r="Q21">
+        <v>1.7613626598761201E-2</v>
+      </c>
+      <c r="R21">
+        <v>7.170753277959026</v>
+      </c>
+      <c r="S21">
+        <v>1.184331263849181E-2</v>
+      </c>
+      <c r="T21">
+        <v>9.8741956129821542</v>
+      </c>
+      <c r="U21">
+        <v>1.7633834550181859E-2</v>
+      </c>
+      <c r="V21">
+        <v>10.25996974240574</v>
+      </c>
+      <c r="W21">
+        <v>1.523214692356412E-2</v>
+      </c>
+      <c r="X21">
+        <v>5.1742099993998973</v>
+      </c>
+      <c r="Y21">
+        <v>-1.0002620783637889E-2</v>
+      </c>
+      <c r="Z21">
+        <v>-1.880988098862252E-3</v>
+      </c>
+      <c r="AA21">
+        <v>-7.231761265959688E-4</v>
+      </c>
+      <c r="AB21">
+        <v>-1.3861434865687641E-4</v>
+      </c>
+      <c r="AC21">
+        <v>-1.9622224065120042E-3</v>
+      </c>
+      <c r="AD21">
+        <v>-1.7136359970632981E-3</v>
+      </c>
+      <c r="AE21">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>44531</v>
+      </c>
+      <c r="B22">
+        <v>2169.81716056</v>
+      </c>
+      <c r="C22">
+        <v>9.1217174736012499E-2</v>
+      </c>
+      <c r="D22">
+        <v>5749.7459773599994</v>
+      </c>
+      <c r="E22">
+        <v>2.502358037668688E-2</v>
+      </c>
+      <c r="F22">
+        <v>1388.26564278</v>
+      </c>
+      <c r="G22">
+        <v>2.809212703118107E-2</v>
+      </c>
+      <c r="H22">
+        <v>19628.150631429999</v>
+      </c>
+      <c r="I22">
+        <v>5.4190274307697628E-2</v>
+      </c>
+      <c r="J22">
+        <v>28935.97941213</v>
+      </c>
+      <c r="K22">
+        <v>4.9919099083422812E-2</v>
+      </c>
+      <c r="L22">
+        <v>2.5</v>
+      </c>
+      <c r="M22">
+        <v>175.225814954611</v>
+      </c>
+      <c r="N22">
+        <v>7.6823981851781653</v>
+      </c>
+      <c r="O22">
+        <v>-1.127758415104374E-3</v>
+      </c>
+      <c r="P22">
+        <v>8.6569109549650918</v>
+      </c>
+      <c r="Q22">
+        <v>1.3935881955438489E-2</v>
+      </c>
+      <c r="R22">
+        <v>7.2358105080431061</v>
+      </c>
+      <c r="S22">
+        <v>6.5057230084080153E-2</v>
+      </c>
+      <c r="T22">
+        <v>9.8847200714940815</v>
+      </c>
+      <c r="U22">
+        <v>1.0524458511927289E-2</v>
+      </c>
+      <c r="V22">
+        <v>10.27284106213493</v>
+      </c>
+      <c r="W22">
+        <v>1.28713197291912E-2</v>
+      </c>
+      <c r="X22">
+        <v>5.273232864679092</v>
+      </c>
+      <c r="Y22">
+        <v>9.9022865279194683E-2</v>
+      </c>
+      <c r="Z22">
+        <v>-7.3179472765729503E-3</v>
+      </c>
+      <c r="AA22">
+        <v>-3.5564972442569021E-3</v>
+      </c>
+      <c r="AB22">
+        <v>-3.209811293999127E-3</v>
+      </c>
+      <c r="AC22">
+        <v>-5.230053467922699E-3</v>
+      </c>
+      <c r="AD22">
+        <v>-5.0736124009502781E-3</v>
+      </c>
+      <c r="AE22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>44562</v>
+      </c>
+      <c r="B23">
+        <v>2163.45077055</v>
+      </c>
+      <c r="C23">
+        <v>9.3923785091879819E-2</v>
+      </c>
+      <c r="D23">
+        <v>5802.8133554100004</v>
+      </c>
+      <c r="E23">
+        <v>2.7455609970888549E-2</v>
+      </c>
+      <c r="F23">
+        <v>1385.66927007</v>
+      </c>
+      <c r="G23">
+        <v>2.9273104979769728E-2</v>
+      </c>
+      <c r="H23">
+        <v>19591.822615789999</v>
+      </c>
+      <c r="I23">
+        <v>5.9054299032267298E-2</v>
+      </c>
+      <c r="J23">
+        <v>28943.756011820002</v>
+      </c>
+      <c r="K23">
+        <v>5.389982758847553E-2</v>
+      </c>
+      <c r="L23">
+        <v>3</v>
+      </c>
+      <c r="M23">
+        <v>177.77595236253299</v>
+      </c>
+      <c r="N23">
+        <v>7.6794598048647984</v>
+      </c>
+      <c r="O23">
+        <v>-2.9383803133669062E-3</v>
+      </c>
+      <c r="P23">
+        <v>8.6660981402079038</v>
+      </c>
+      <c r="Q23">
+        <v>9.1871852428120349E-3</v>
+      </c>
+      <c r="R23">
+        <v>7.2339385293920007</v>
+      </c>
+      <c r="S23">
+        <v>-1.8719786511054439E-3</v>
+      </c>
+      <c r="T23">
+        <v>9.8828675446807477</v>
+      </c>
+      <c r="U23">
+        <v>-1.85252681333381E-3</v>
+      </c>
+      <c r="V23">
+        <v>10.27310977793606</v>
+      </c>
+      <c r="W23">
+        <v>2.6871580112874938E-4</v>
+      </c>
+      <c r="X23">
+        <v>5.1119546552775281</v>
+      </c>
+      <c r="Y23">
+        <v>-0.1612782094015639</v>
+      </c>
+      <c r="Z23">
+        <v>2.7066103558673199E-3</v>
+      </c>
+      <c r="AA23">
+        <v>2.4320295942016688E-3</v>
+      </c>
+      <c r="AB23">
+        <v>1.1809779485886589E-3</v>
+      </c>
+      <c r="AC23">
+        <v>4.8640247245696697E-3</v>
+      </c>
+      <c r="AD23">
+        <v>3.9807285050527177E-3</v>
+      </c>
+      <c r="AE23">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>44593</v>
+      </c>
+      <c r="B24">
+        <v>2159.5255895599998</v>
+      </c>
+      <c r="C24">
+        <v>9.7333164277449757E-2</v>
+      </c>
+      <c r="D24">
+        <v>5914.4869055199997</v>
+      </c>
+      <c r="E24">
+        <v>2.795292140822898E-2</v>
+      </c>
+      <c r="F24">
+        <v>1394.5299547</v>
+      </c>
+      <c r="G24">
+        <v>2.907100487398372E-2</v>
+      </c>
+      <c r="H24">
+        <v>19819.768310349999</v>
+      </c>
+      <c r="I24">
+        <v>6.09586301843437E-2</v>
+      </c>
+      <c r="J24">
+        <v>29288.31076013</v>
+      </c>
+      <c r="K24">
+        <v>5.5457174495057507E-2</v>
+      </c>
+      <c r="L24">
+        <v>3.5</v>
+      </c>
+      <c r="M24">
+        <v>177.45500302739299</v>
+      </c>
+      <c r="N24">
+        <v>7.677643842092067</v>
+      </c>
+      <c r="O24">
+        <v>-1.8159627727314389E-3</v>
+      </c>
+      <c r="P24">
+        <v>8.6851600280210448</v>
+      </c>
+      <c r="Q24">
+        <v>1.9061887813140999E-2</v>
+      </c>
+      <c r="R24">
+        <v>7.2403126874392054</v>
+      </c>
+      <c r="S24">
+        <v>6.3741580472047588E-3</v>
+      </c>
+      <c r="T24">
+        <v>9.894435118125946</v>
+      </c>
+      <c r="U24">
+        <v>1.156757344519832E-2</v>
+      </c>
+      <c r="V24">
+        <v>10.284943765237159</v>
+      </c>
+      <c r="W24">
+        <v>1.183398730109886E-2</v>
+      </c>
+      <c r="X24">
+        <v>5.0956937097421706</v>
+      </c>
+      <c r="Y24">
+        <v>-1.6260945535357511E-2</v>
+      </c>
+      <c r="Z24">
+        <v>3.409379185569938E-3</v>
+      </c>
+      <c r="AA24">
+        <v>4.9731143734043151E-4</v>
+      </c>
+      <c r="AB24">
+        <v>-2.0210010578600859E-4</v>
+      </c>
+      <c r="AC24">
+        <v>1.904331152076402E-3</v>
+      </c>
+      <c r="AD24">
+        <v>1.5573469065819771E-3</v>
+      </c>
+      <c r="AE24">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>44621</v>
+      </c>
+      <c r="B25">
+        <v>2154.9887514900001</v>
+      </c>
+      <c r="C25">
+        <v>9.9443574817654645E-2</v>
+      </c>
+      <c r="D25">
+        <v>6025.3310061599996</v>
+      </c>
+      <c r="E25">
+        <v>2.7902767824393208E-2</v>
+      </c>
+      <c r="F25">
+        <v>1402.4647080100001</v>
+      </c>
+      <c r="G25">
+        <v>2.8875945946235711E-2</v>
+      </c>
+      <c r="H25">
+        <v>20139.74479144</v>
+      </c>
+      <c r="I25">
+        <v>6.1288311514484932E-2</v>
+      </c>
+      <c r="J25">
+        <v>29722.529257099999</v>
+      </c>
+      <c r="K25">
+        <v>5.5757423287727863E-2</v>
+      </c>
+      <c r="L25">
+        <v>4</v>
+      </c>
+      <c r="M25">
+        <v>175.624506747689</v>
+      </c>
+      <c r="N25">
+        <v>7.6755407827980084</v>
+      </c>
+      <c r="O25">
+        <v>-2.1030592940594062E-3</v>
+      </c>
+      <c r="P25">
+        <v>8.7037276956315193</v>
+      </c>
+      <c r="Q25">
+        <v>1.8567667610474459E-2</v>
+      </c>
+      <c r="R25">
+        <v>7.2459864734510084</v>
+      </c>
+      <c r="S25">
+        <v>5.673786011803017E-3</v>
+      </c>
+      <c r="T25">
+        <v>9.9104504944663478</v>
+      </c>
+      <c r="U25">
+        <v>1.601537634040184E-2</v>
+      </c>
+      <c r="V25">
+        <v>10.299660598074039</v>
+      </c>
+      <c r="W25">
+        <v>1.4716832836885629E-2</v>
+      </c>
+      <c r="X25">
+        <v>5.1444672248879924</v>
+      </c>
+      <c r="Y25">
+        <v>4.8773515145821733E-2</v>
+      </c>
+      <c r="Z25">
+        <v>2.1104105402048878E-3</v>
+      </c>
+      <c r="AA25">
+        <v>-5.0153583835772092E-5</v>
+      </c>
+      <c r="AB25">
+        <v>-1.9505892774800829E-4</v>
+      </c>
+      <c r="AC25">
+        <v>3.2968133014123208E-4</v>
+      </c>
+      <c r="AD25">
+        <v>3.0024879267035592E-4</v>
+      </c>
+      <c r="AE25">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>44652</v>
+      </c>
+      <c r="B26">
+        <v>2160.2823818900001</v>
+      </c>
+      <c r="C26">
+        <v>0.10388968486779419</v>
+      </c>
+      <c r="D26">
+        <v>6109.3115564</v>
+      </c>
+      <c r="E26">
+        <v>2.7698388439975741E-2</v>
+      </c>
+      <c r="F26">
+        <v>1409.32815132</v>
+      </c>
+      <c r="G26">
+        <v>2.899783176240598E-2</v>
+      </c>
+      <c r="H26">
+        <v>20322.691519280001</v>
+      </c>
+      <c r="I26">
+        <v>6.1166226027724493E-2</v>
+      </c>
+      <c r="J26">
+        <v>30001.613608889998</v>
+      </c>
+      <c r="K26">
+        <v>5.5916290567881458E-2</v>
+      </c>
+      <c r="L26">
+        <v>4.5</v>
+      </c>
+      <c r="M26">
+        <v>175.36384503404199</v>
+      </c>
+      <c r="N26">
+        <v>7.6779942244899626</v>
+      </c>
+      <c r="O26">
+        <v>2.453441691955049E-3</v>
+      </c>
+      <c r="P26">
+        <v>8.7175693709237319</v>
+      </c>
+      <c r="Q26">
+        <v>1.384167529221259E-2</v>
+      </c>
+      <c r="R26">
+        <v>7.2508683813899983</v>
+      </c>
+      <c r="S26">
+        <v>4.8819079389899036E-3</v>
+      </c>
+      <c r="T26">
+        <v>9.9194933495782909</v>
+      </c>
+      <c r="U26">
+        <v>9.0428551119430267E-3</v>
+      </c>
+      <c r="V26">
+        <v>10.309006446160829</v>
+      </c>
+      <c r="W26">
+        <v>9.3458480867827376E-3</v>
+      </c>
+      <c r="X26">
+        <v>5.1434736132675161</v>
+      </c>
+      <c r="Y26">
+        <v>-9.9361162047628682E-4</v>
+      </c>
+      <c r="Z26">
+        <v>4.4461100501395484E-3</v>
+      </c>
+      <c r="AA26">
+        <v>-2.043793844174677E-4</v>
+      </c>
+      <c r="AB26">
+        <v>1.218858161702689E-4</v>
+      </c>
+      <c r="AC26">
+        <v>-1.2208548676043851E-4</v>
+      </c>
+      <c r="AD26">
+        <v>1.588672801535948E-4</v>
+      </c>
+      <c r="AE26">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>44682</v>
+      </c>
+      <c r="B27">
+        <v>2154.5626099599999</v>
+      </c>
+      <c r="C27">
+        <v>0.1014939018476979</v>
+      </c>
+      <c r="D27">
+        <v>6210.7306745899996</v>
+      </c>
+      <c r="E27">
+        <v>2.7251930952741449E-2</v>
+      </c>
+      <c r="F27">
+        <v>1469.05325739</v>
+      </c>
+      <c r="G27">
+        <v>4.2067353759383641E-2</v>
+      </c>
+      <c r="H27">
+        <v>20483.47195363</v>
+      </c>
+      <c r="I27">
+        <v>5.9320679424401293E-2</v>
+      </c>
+      <c r="J27">
+        <v>30317.818495570002</v>
+      </c>
+      <c r="K27">
+        <v>5.4912329069562227E-2</v>
+      </c>
+      <c r="L27">
+        <v>5</v>
+      </c>
+      <c r="M27">
+        <v>176.549094020246</v>
+      </c>
+      <c r="N27">
+        <v>7.6753430167218442</v>
+      </c>
+      <c r="O27">
+        <v>-2.6512077681184461E-3</v>
+      </c>
+      <c r="P27">
+        <v>8.7340338289705901</v>
+      </c>
+      <c r="Q27">
+        <v>1.6464458046858251E-2</v>
+      </c>
+      <c r="R27">
+        <v>7.2923734296964247</v>
+      </c>
+      <c r="S27">
+        <v>4.1505048306426318E-2</v>
+      </c>
+      <c r="T27">
+        <v>9.92737359377087</v>
+      </c>
+      <c r="U27">
+        <v>7.8802441925791555E-3</v>
+      </c>
+      <c r="V27">
+        <v>10.319490887813281</v>
+      </c>
+      <c r="W27">
+        <v>1.0484441652451441E-2</v>
+      </c>
+      <c r="X27">
+        <v>5.1923644532351414</v>
+      </c>
+      <c r="Y27">
+        <v>4.8890839967625332E-2</v>
+      </c>
+      <c r="Z27">
+        <v>-2.3957830200962982E-3</v>
+      </c>
+      <c r="AA27">
+        <v>-4.4645748723429191E-4</v>
+      </c>
+      <c r="AB27">
+        <v>1.3069521996977661E-2</v>
+      </c>
+      <c r="AC27">
+        <v>-1.8455466033232E-3</v>
+      </c>
+      <c r="AD27">
+        <v>-1.003961498319231E-3</v>
+      </c>
+      <c r="AE27">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>44713</v>
+      </c>
+      <c r="B28">
+        <v>2171.5867223400001</v>
+      </c>
+      <c r="C28">
+        <v>0.1021520059079033</v>
+      </c>
+      <c r="D28">
+        <v>6276.0739399699996</v>
+      </c>
+      <c r="E28">
+        <v>2.6874319215048351E-2</v>
+      </c>
+      <c r="F28">
+        <v>1473.95082613</v>
+      </c>
+      <c r="G28">
+        <v>4.1859331021236047E-2</v>
+      </c>
+      <c r="H28">
+        <v>20658.609303699999</v>
+      </c>
+      <c r="I28">
+        <v>5.8381463019584218E-2</v>
+      </c>
+      <c r="J28">
+        <v>30580.22079214</v>
+      </c>
+      <c r="K28">
+        <v>5.4227063829317558E-2</v>
+      </c>
+      <c r="L28">
+        <v>5.5</v>
+      </c>
+      <c r="M28">
+        <v>179.22937448249701</v>
+      </c>
+      <c r="N28">
+        <v>7.6832133877834643</v>
+      </c>
+      <c r="O28">
+        <v>7.8703710616201406E-3</v>
+      </c>
+      <c r="P28">
+        <v>8.744499895168163</v>
+      </c>
+      <c r="Q28">
+        <v>1.046606619757284E-2</v>
+      </c>
+      <c r="R28">
+        <v>7.2957017113583316</v>
+      </c>
+      <c r="S28">
+        <v>3.3282816619077948E-3</v>
+      </c>
+      <c r="T28">
+        <v>9.9358874269375015</v>
+      </c>
+      <c r="U28">
+        <v>8.5138331666314571E-3</v>
+      </c>
+      <c r="V28">
+        <v>10.328108699605449</v>
+      </c>
+      <c r="W28">
+        <v>8.6178117921740238E-3</v>
+      </c>
+      <c r="X28">
+        <v>5.1842933195331096</v>
+      </c>
+      <c r="Y28">
+        <v>-8.0711337020318297E-3</v>
+      </c>
+      <c r="Z28">
+        <v>6.581040602054028E-4</v>
+      </c>
+      <c r="AA28">
+        <v>-3.776117376930975E-4</v>
+      </c>
+      <c r="AB28">
+        <v>-2.0802273814759381E-4</v>
+      </c>
+      <c r="AC28">
+        <v>-9.3921640481707536E-4</v>
+      </c>
+      <c r="AD28">
+        <v>-6.8526524024466878E-4</v>
+      </c>
+      <c r="AE28">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>44743</v>
+      </c>
+      <c r="B29">
+        <v>2167.5417105699999</v>
+      </c>
+      <c r="C29">
+        <v>0.1105223508372544</v>
+      </c>
+      <c r="D29">
+        <v>6331.3028230299997</v>
+      </c>
+      <c r="E29">
+        <v>2.7757695861701681E-2</v>
+      </c>
+      <c r="F29">
+        <v>1477.4233848900001</v>
+      </c>
+      <c r="G29">
+        <v>4.1208457787158252E-2</v>
+      </c>
+      <c r="H29">
+        <v>20863.02957418</v>
+      </c>
+      <c r="I29">
+        <v>5.9807626479340903E-2</v>
+      </c>
+      <c r="J29">
+        <v>30839.297492670001</v>
+      </c>
+      <c r="K29">
+        <v>5.5901234558269557E-2</v>
+      </c>
+      <c r="L29">
+        <v>6</v>
+      </c>
+      <c r="M29">
+        <v>177.76735736691001</v>
+      </c>
+      <c r="N29">
+        <v>7.6813489521004517</v>
+      </c>
+      <c r="O29">
+        <v>-1.8644356830126441E-3</v>
+      </c>
+      <c r="P29">
+        <v>8.7532613111850921</v>
+      </c>
+      <c r="Q29">
+        <v>8.7614160169291466E-3</v>
+      </c>
+      <c r="R29">
+        <v>7.2980548933773832</v>
+      </c>
+      <c r="S29">
+        <v>2.3531820190507702E-3</v>
+      </c>
+      <c r="T29">
+        <v>9.9457339516709293</v>
+      </c>
+      <c r="U29">
+        <v>9.8465247334278416E-3</v>
+      </c>
+      <c r="V29">
+        <v>10.33654504832151</v>
+      </c>
+      <c r="W29">
+        <v>8.4363487160636907E-3</v>
+      </c>
+      <c r="X29">
+        <v>5.1814829433165821</v>
+      </c>
+      <c r="Y29">
+        <v>-2.8103762165274659E-3</v>
+      </c>
+      <c r="Z29">
+        <v>8.3703449293510979E-3</v>
+      </c>
+      <c r="AA29">
+        <v>8.8337664665332979E-4</v>
+      </c>
+      <c r="AB29">
+        <v>-6.5087323407779507E-4</v>
+      </c>
+      <c r="AC29">
+        <v>1.426163459756685E-3</v>
+      </c>
+      <c r="AD29">
+        <v>1.674170728951999E-3</v>
+      </c>
+      <c r="AE29">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>44774</v>
+      </c>
+      <c r="B30">
+        <v>2183.1975619300001</v>
+      </c>
+      <c r="C30">
+        <v>0.11121653208761929</v>
+      </c>
+      <c r="D30">
+        <v>6404.7049425300002</v>
+      </c>
+      <c r="E30">
+        <v>2.750088030915953E-2</v>
+      </c>
+      <c r="F30">
+        <v>1487.36756025</v>
+      </c>
+      <c r="G30">
+        <v>4.0985748815009493E-2</v>
+      </c>
+      <c r="H30">
+        <v>21115.346774969999</v>
+      </c>
+      <c r="I30">
+        <v>6.0149252036226841E-2</v>
+      </c>
+      <c r="J30">
+        <v>31190.616839679999</v>
+      </c>
+      <c r="K30">
+        <v>5.6105843720721811E-2</v>
+      </c>
+      <c r="L30">
+        <v>6.5</v>
+      </c>
+      <c r="M30">
+        <v>177.59760674853001</v>
+      </c>
+      <c r="N30">
+        <v>7.6885458526520249</v>
+      </c>
+      <c r="O30">
+        <v>7.1969005515732931E-3</v>
+      </c>
+      <c r="P30">
+        <v>8.7647881465296837</v>
+      </c>
+      <c r="Q30">
+        <v>1.152683534459165E-2</v>
+      </c>
+      <c r="R30">
+        <v>7.3047630983298726</v>
+      </c>
+      <c r="S30">
+        <v>6.7082049524893614E-3</v>
+      </c>
+      <c r="T30">
+        <v>9.9577553903906555</v>
+      </c>
+      <c r="U30">
+        <v>1.2021438719726159E-2</v>
+      </c>
+      <c r="V30">
+        <v>10.347872586247581</v>
+      </c>
+      <c r="W30">
+        <v>1.132753792606955E-2</v>
+      </c>
+      <c r="X30">
+        <v>5.1875924883910596</v>
+      </c>
+      <c r="Y30">
+        <v>6.1095450744774737E-3</v>
+      </c>
+      <c r="Z30">
+        <v>6.9418125036489753E-4</v>
+      </c>
+      <c r="AA30">
+        <v>-2.5681555254215138E-4</v>
+      </c>
+      <c r="AB30">
+        <v>-2.2270897214875929E-4</v>
+      </c>
+      <c r="AC30">
+        <v>3.4162555688593832E-4</v>
+      </c>
+      <c r="AD30">
+        <v>2.0460916245225449E-4</v>
+      </c>
+      <c r="AE30">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>44805</v>
+      </c>
+      <c r="B31">
+        <v>2199.7633651400001</v>
+      </c>
+      <c r="C31">
+        <v>0.10735566742424139</v>
+      </c>
+      <c r="D31">
+        <v>6489.5910629800001</v>
+      </c>
+      <c r="E31">
+        <v>2.7683018923153009E-2</v>
+      </c>
+      <c r="F31">
+        <v>1497.1359020499999</v>
+      </c>
+      <c r="G31">
+        <v>3.972146793659212E-2</v>
+      </c>
+      <c r="H31">
+        <v>21407.916797350001</v>
+      </c>
+      <c r="I31">
+        <v>6.1088183416888257E-2</v>
+      </c>
+      <c r="J31">
+        <v>31594.40712752</v>
+      </c>
+      <c r="K31">
+        <v>5.6435549268683501E-2</v>
+      </c>
+      <c r="L31">
+        <v>6.75</v>
+      </c>
+      <c r="M31">
+        <v>179.26037297873199</v>
+      </c>
+      <c r="N31">
+        <v>7.6961050722612754</v>
+      </c>
+      <c r="O31">
+        <v>7.5592196092504338E-3</v>
+      </c>
+      <c r="P31">
+        <v>8.7779547973862453</v>
+      </c>
+      <c r="Q31">
+        <v>1.3166650856561549E-2</v>
+      </c>
+      <c r="R31">
+        <v>7.3113091632316394</v>
+      </c>
+      <c r="S31">
+        <v>6.5460649017667896E-3</v>
+      </c>
+      <c r="T31">
+        <v>9.9715160763990092</v>
+      </c>
+      <c r="U31">
+        <v>1.376068600835367E-2</v>
+      </c>
+      <c r="V31">
+        <v>10.36073539427505</v>
+      </c>
+      <c r="W31">
+        <v>1.286280802746198E-2</v>
+      </c>
+      <c r="X31">
+        <v>5.2052059676522777</v>
+      </c>
+      <c r="Y31">
+        <v>1.7613479261218149E-2</v>
+      </c>
+      <c r="Z31">
+        <v>-3.8608646633778998E-3</v>
+      </c>
+      <c r="AA31">
+        <v>1.8213861399347939E-4</v>
+      </c>
+      <c r="AB31">
+        <v>-1.2642808784173729E-3</v>
+      </c>
+      <c r="AC31">
+        <v>9.3893138066141607E-4</v>
+      </c>
+      <c r="AD31">
+        <v>3.2970554796168949E-4</v>
+      </c>
+      <c r="AE31">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>44835</v>
+      </c>
+      <c r="B32">
+        <v>2203.08783657</v>
+      </c>
+      <c r="C32">
+        <v>0.1167990055996227</v>
+      </c>
+      <c r="D32">
+        <v>6579.0635725500006</v>
+      </c>
+      <c r="E32">
+        <v>2.768095673065727E-2</v>
+      </c>
+      <c r="F32">
+        <v>1505.2793700499999</v>
+      </c>
+      <c r="G32">
+        <v>3.9623908097550557E-2</v>
+      </c>
+      <c r="H32">
+        <v>21706.975802270001</v>
+      </c>
+      <c r="I32">
+        <v>6.3164004349081995E-2</v>
+      </c>
+      <c r="J32">
+        <v>31994.406581439998</v>
+      </c>
+      <c r="K32">
+        <v>5.8453273802080541E-2</v>
+      </c>
+      <c r="L32">
+        <v>7</v>
+      </c>
+      <c r="M32">
+        <v>178.96693481014299</v>
+      </c>
+      <c r="N32">
+        <v>7.6976152173511254</v>
+      </c>
+      <c r="O32">
+        <v>1.510145089849146E-3</v>
+      </c>
+      <c r="P32">
+        <v>8.7916476999896087</v>
+      </c>
+      <c r="Q32">
+        <v>1.369290260336342E-2</v>
+      </c>
+      <c r="R32">
+        <v>7.3167337878964407</v>
+      </c>
+      <c r="S32">
+        <v>5.4246246648013141E-3</v>
+      </c>
+      <c r="T32">
+        <v>9.9853889534119702</v>
+      </c>
+      <c r="U32">
+        <v>1.387287701296103E-2</v>
+      </c>
+      <c r="V32">
+        <v>10.37331637217356</v>
+      </c>
+      <c r="W32">
+        <v>1.258097789850865E-2</v>
+      </c>
+      <c r="X32">
+        <v>5.2100373670151896</v>
+      </c>
+      <c r="Y32">
+        <v>4.8313993629118812E-3</v>
+      </c>
+      <c r="Z32">
+        <v>9.4433381753813023E-3</v>
+      </c>
+      <c r="AA32">
+        <v>-2.062192495738691E-6</v>
+      </c>
+      <c r="AB32">
+        <v>-9.7559839041562457E-5</v>
+      </c>
+      <c r="AC32">
+        <v>2.0758209321937379E-3</v>
+      </c>
+      <c r="AD32">
+        <v>2.0177245333970399E-3</v>
+      </c>
+      <c r="AE32">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>44866</v>
+      </c>
+      <c r="B33">
+        <v>2208.6535991800001</v>
+      </c>
+      <c r="C33">
+        <v>0.112432755178175</v>
+      </c>
+      <c r="D33">
+        <v>6676.3844705000001</v>
+      </c>
+      <c r="E33">
+        <v>2.7402804257062E-2</v>
+      </c>
+      <c r="F33">
+        <v>1508.91184572</v>
+      </c>
+      <c r="G33">
+        <v>3.9345624257904312E-2</v>
+      </c>
+      <c r="H33">
+        <v>22105.60582493</v>
+      </c>
+      <c r="I33">
+        <v>6.4014908517191979E-2</v>
+      </c>
+      <c r="J33">
+        <v>32499.555740330001</v>
+      </c>
+      <c r="K33">
+        <v>5.8638773235139899E-2</v>
+      </c>
+      <c r="L33">
+        <v>7.25</v>
+      </c>
+      <c r="M33">
+        <v>177.723455970728</v>
+      </c>
+      <c r="N33">
+        <v>7.7001383777148256</v>
+      </c>
+      <c r="O33">
+        <v>2.5231603637019262E-3</v>
+      </c>
+      <c r="P33">
+        <v>8.8063318730725602</v>
+      </c>
+      <c r="Q33">
+        <v>1.468417308295145E-2</v>
+      </c>
+      <c r="R33">
+        <v>7.3191440380554278</v>
+      </c>
+      <c r="S33">
+        <v>2.4102501589871039E-3</v>
+      </c>
+      <c r="T33">
+        <v>10.003586512576939</v>
+      </c>
+      <c r="U33">
+        <v>1.8197559164967458E-2</v>
+      </c>
+      <c r="V33">
+        <v>10.388981698696091</v>
+      </c>
+      <c r="W33">
+        <v>1.5665326522537271E-2</v>
+      </c>
+      <c r="X33">
+        <v>5.1961971509984943</v>
+      </c>
+      <c r="Y33">
+        <v>-1.3840216016695271E-2</v>
+      </c>
+      <c r="Z33">
+        <v>-4.3662504214476983E-3</v>
+      </c>
+      <c r="AA33">
+        <v>-2.781524735952709E-4</v>
+      </c>
+      <c r="AB33">
+        <v>-2.7828383964624559E-4</v>
+      </c>
+      <c r="AC33">
+        <v>8.5090416810998382E-4</v>
+      </c>
+      <c r="AD33">
+        <v>1.854994330593579E-4</v>
+      </c>
+      <c r="AE33">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>44896</v>
+      </c>
+      <c r="B34">
+        <v>2234.6737479899998</v>
+      </c>
+      <c r="C34">
+        <v>0.1029223141037361</v>
+      </c>
+      <c r="D34">
+        <v>6749.00415419</v>
+      </c>
+      <c r="E34">
+        <v>2.541808343879863E-2</v>
+      </c>
+      <c r="F34">
+        <v>1513.8221178900001</v>
+      </c>
+      <c r="G34">
+        <v>3.7173050779859877E-2</v>
+      </c>
+      <c r="H34">
+        <v>22169.33574626</v>
+      </c>
+      <c r="I34">
+        <v>5.8095715359323653E-2</v>
+      </c>
+      <c r="J34">
+        <v>32666.835766330001</v>
+      </c>
+      <c r="K34">
+        <v>5.3441397333297017E-2</v>
+      </c>
+      <c r="L34">
+        <v>7.5</v>
+      </c>
+      <c r="M34">
+        <v>178.01322374453099</v>
+      </c>
+      <c r="N34">
+        <v>7.7118505223387288</v>
+      </c>
+      <c r="O34">
+        <v>1.1712144623902351E-2</v>
+      </c>
+      <c r="P34">
+        <v>8.817150240269962</v>
+      </c>
+      <c r="Q34">
+        <v>1.0818367197401811E-2</v>
+      </c>
+      <c r="R34">
+        <v>7.3223929356085993</v>
+      </c>
+      <c r="S34">
+        <v>3.248897553171481E-3</v>
+      </c>
+      <c r="T34">
+        <v>10.006465340332889</v>
+      </c>
+      <c r="U34">
+        <v>2.878827755957047E-3</v>
+      </c>
+      <c r="V34">
+        <v>10.39411564549151</v>
+      </c>
+      <c r="W34">
+        <v>5.1339467954143458E-3</v>
+      </c>
+      <c r="X34">
+        <v>5.286361175301324</v>
+      </c>
+      <c r="Y34">
+        <v>9.016402430282966E-2</v>
+      </c>
+      <c r="Z34">
+        <v>-9.510441074438894E-3</v>
+      </c>
+      <c r="AA34">
+        <v>-1.9847208182633691E-3</v>
+      </c>
+      <c r="AB34">
+        <v>-2.172573478044434E-3</v>
+      </c>
+      <c r="AC34">
+        <v>-5.9191931578683257E-3</v>
+      </c>
+      <c r="AD34">
+        <v>-5.1973759018428822E-3</v>
+      </c>
+      <c r="AE34">
+        <v>0.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDFF7303-AF0A-4985-B3CA-77BE283E0624}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:D253"/>
